--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_42.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3270784.998985186</v>
+        <v>3271948.813194895</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13690477.8518317</v>
+        <v>13633690.08805689</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13690477.8518317</v>
+        <v>13633690.08805689</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160451.2332570993</v>
+        <v>143186.9484571651</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160451.2332570993</v>
+        <v>143186.9484571651</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25062605.13013608</v>
+        <v>25064260.45115706</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3392818347549</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.727889859306288</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.42905667517471</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T2" t="n">
-        <v>184.84539077379</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1878493124298</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4244990988957</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,25 +778,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.5243971659513</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.3848916320019</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>149.3388625564148</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
+        <v>4.464774651476091</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1957842884886531</v>
+      </c>
+      <c r="V3" t="n">
+        <v>172.4047620250126</v>
+      </c>
+      <c r="W3" t="n">
         <v>374</v>
-      </c>
-      <c r="U3" t="n">
-        <v>374</v>
-      </c>
-      <c r="V3" t="n">
-        <v>14.51066719152016</v>
-      </c>
-      <c r="W3" t="n">
-        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.23370976320564</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>142.4861900257832</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>213.9374985052444</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>264.7656678200808</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.135266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.1696033909872</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.339281834754904</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H5" t="n">
-        <v>3.727889859306304</v>
+        <v>3.769060713577661</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.108125053756319</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.32093162141838</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
-        <v>184.84539077379</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1878493124298</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -973,25 +973,25 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.5532638959642</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.3848916320019</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S6" t="n">
-        <v>62.40890562498866</v>
+        <v>374</v>
       </c>
       <c r="T6" t="n">
-        <v>4.456104840155326</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1956427790546723</v>
+        <v>332.964557871017</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.23370976320562</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N7" t="n">
-        <v>142.4861900257833</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>213.9374985052445</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>264.7656678200808</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.135266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.1696033909871</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3392818347549</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.727889859306288</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.42905667517471</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T8" t="n">
-        <v>184.84539077379</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1878493124298</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>109.490950793667</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.3848916320019</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.40890562498868</v>
+        <v>221.6521733747632</v>
       </c>
       <c r="T9" t="n">
-        <v>4.456104840155319</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1956427790546513</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.23370976320564</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>142.4861900257832</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>213.9374985052444</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>264.7656678200808</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.135266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.1696033909872</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H11" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.388898923102697</v>
       </c>
       <c r="S11" t="n">
-        <v>143.1742526550738</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T11" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1453,16 +1453,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>196.7134233626615</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H12" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.532287858417</v>
+        <v>372.2590055347304</v>
       </c>
       <c r="S12" t="n">
-        <v>131.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T12" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1513,7 +1513,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M13" t="n">
         <v>100.6963655009106</v>
@@ -1574,7 +1574,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S13" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>72.59985970855254</v>
       </c>
       <c r="I14" t="n">
-        <v>1.388898923102739</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.388898923102697</v>
       </c>
       <c r="S14" t="n">
         <v>141.7853537319711</v>
@@ -1684,16 +1684,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>232.8266301218324</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>3.986705686348098</v>
@@ -1738,16 +1738,16 @@
         <v>81.32333125524967</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16083145829995</v>
+        <v>271.8875491346131</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>78.39139276613435</v>
@@ -1857,10 +1857,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H17" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.388898923102767</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,16 +1887,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.388898923102697</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T17" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U17" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1921,22 +1921,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>196.7134233626614</v>
+        <v>196.7134233626611</v>
       </c>
       <c r="H18" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T18" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
@@ -1984,7 +1984,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M19" t="n">
         <v>100.6963655009106</v>
@@ -2048,7 +2048,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S19" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.388898923102697</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.7853537319712</v>
+        <v>143.1742526550738</v>
       </c>
       <c r="T20" t="n">
         <v>259.5162852461518</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>256.2832743226397</v>
       </c>
       <c r="C21" t="n">
         <v>40.09991244551929</v>
@@ -2170,7 +2170,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>196.7134233626611</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H21" t="n">
         <v>3.897332469440016</v>
@@ -2331,7 +2331,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H23" t="n">
-        <v>73.98875863165527</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.388898923102697</v>
       </c>
       <c r="S23" t="n">
         <v>141.7853537319712</v>
@@ -2395,13 +2395,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>232.8266301218324</v>
+        <v>232.8266301218325</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -2461,7 +2461,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2571,7 +2571,7 @@
         <v>72.59985970855254</v>
       </c>
       <c r="I26" t="n">
-        <v>5.269698923102741</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S26" t="n">
         <v>141.7853537319711</v>
@@ -2635,10 +2635,10 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>181.0524309641367</v>
+        <v>181.0524309641363</v>
       </c>
       <c r="S27" t="n">
         <v>131.5805093985736</v>
@@ -2689,7 +2689,7 @@
         <v>79.16083145829995</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
         <v>432.3731429098285</v>
@@ -2698,7 +2698,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2808,7 +2808,7 @@
         <v>72.59985970855254</v>
       </c>
       <c r="I29" t="n">
-        <v>5.269698923102741</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S29" t="n">
         <v>141.7853537319711</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
@@ -2884,10 +2884,10 @@
         <v>3.986705686348098</v>
       </c>
       <c r="H30" t="n">
-        <v>324.89733246944</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I30" t="n">
-        <v>115.745565793381</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>179.532287858417</v>
@@ -2923,16 +2923,16 @@
         <v>81.32333125524967</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16083145829995</v>
+        <v>271.8875491346131</v>
       </c>
       <c r="V30" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -3042,10 +3042,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H32" t="n">
-        <v>72.59985970855251</v>
+        <v>77.86955863165528</v>
       </c>
       <c r="I32" t="n">
-        <v>5.269698923102768</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3106,16 +3106,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>232.8266301218324</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>211.36296001419</v>
       </c>
       <c r="G33" t="n">
         <v>3.986705686348103</v>
@@ -3166,10 +3166,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>133.9993129555745</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>101.4745782429939</v>
+        <v>104.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>62.33915573984979</v>
+        <v>65.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>56.36328960686865</v>
+        <v>59.36328960686865</v>
       </c>
       <c r="F35" t="n">
-        <v>56.88962870801186</v>
+        <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>41.77843603433569</v>
+        <v>45.46723603428197</v>
       </c>
       <c r="H35" t="n">
-        <v>45.59985970855254</v>
+        <v>48.59985970855254</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>114.7853537319711</v>
+        <v>117.7853537319711</v>
       </c>
       <c r="T35" t="n">
-        <v>232.5162852461518</v>
+        <v>235.5162852461518</v>
       </c>
       <c r="U35" t="n">
-        <v>301.1087337345403</v>
+        <v>304.1087337345403</v>
       </c>
       <c r="V35" t="n">
-        <v>281.8510241668239</v>
+        <v>284.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>290.3734759809475</v>
+        <v>293.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>244.2818334606677</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>163.3174326828064</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>36.55655664632661</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>61.0410021673467</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>152.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S36" t="n">
-        <v>104.5805093985736</v>
+        <v>184.3103115658671</v>
       </c>
       <c r="T36" t="n">
-        <v>54.32333125524966</v>
+        <v>57.32333125524966</v>
       </c>
       <c r="U36" t="n">
-        <v>52.16083145829995</v>
+        <v>55.16083145829995</v>
       </c>
       <c r="V36" t="n">
-        <v>66.51066719152016</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>84.37314290982852</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>71.86273944538755</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>51.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>73.69636550091056</v>
+        <v>76.69636550091056</v>
       </c>
       <c r="N37" t="n">
-        <v>126.602288386439</v>
+        <v>129.602288386439</v>
       </c>
       <c r="O37" t="n">
-        <v>203.2357280134412</v>
+        <v>206.2357280134412</v>
       </c>
       <c r="P37" t="n">
-        <v>263.1134710987693</v>
+        <v>266.1134710987693</v>
       </c>
       <c r="Q37" t="n">
-        <v>324.989266425598</v>
+        <v>327.989266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>350.2234394565609</v>
+        <v>353.2234394565609</v>
       </c>
       <c r="S37" t="n">
-        <v>3.374299374986586</v>
+        <v>6.374299374986586</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>133.9993129555745</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>101.4745782429939</v>
+        <v>104.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>62.33915573984979</v>
+        <v>65.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>56.36328960686865</v>
+        <v>59.36328960686865</v>
       </c>
       <c r="F38" t="n">
-        <v>56.88962870801186</v>
+        <v>59.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>54.35033711113682</v>
+        <v>57.35033711113681</v>
       </c>
       <c r="H38" t="n">
-        <v>45.59985970855254</v>
+        <v>36.71675863175442</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,28 +3546,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>-5.366314420648614e-11</v>
       </c>
       <c r="S38" t="n">
-        <v>102.21345265517</v>
+        <v>117.7853537319712</v>
       </c>
       <c r="T38" t="n">
-        <v>232.5162852461518</v>
+        <v>235.5162852461518</v>
       </c>
       <c r="U38" t="n">
-        <v>301.1087337345403</v>
+        <v>304.1087337345404</v>
       </c>
       <c r="V38" t="n">
-        <v>281.8510241668239</v>
+        <v>284.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>290.3734759809475</v>
+        <v>293.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>244.2818334606677</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>163.3174326828064</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3577,28 +3577,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>36.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>13.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H39" t="n">
-        <v>217.8344275967531</v>
+        <v>91.37933881882199</v>
       </c>
       <c r="I39" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,28 +3625,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>152.532287858417</v>
+        <v>155.532287858417</v>
       </c>
       <c r="S39" t="n">
-        <v>104.5805093985736</v>
+        <v>107.5805093985736</v>
       </c>
       <c r="T39" t="n">
-        <v>54.32333125524966</v>
+        <v>57.32333125524968</v>
       </c>
       <c r="U39" t="n">
-        <v>52.16083145829995</v>
+        <v>55.16083145829998</v>
       </c>
       <c r="V39" t="n">
-        <v>66.51066719152016</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>84.37314290982852</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>71.86273944538755</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>51.39139276613435</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3689,25 +3689,25 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>73.69636550091056</v>
+        <v>76.69636550091059</v>
       </c>
       <c r="N40" t="n">
-        <v>126.602288386439</v>
+        <v>129.602288386439</v>
       </c>
       <c r="O40" t="n">
-        <v>203.2357280134412</v>
+        <v>206.2357280134412</v>
       </c>
       <c r="P40" t="n">
-        <v>263.1134710987693</v>
+        <v>266.1134710987693</v>
       </c>
       <c r="Q40" t="n">
-        <v>324.989266425598</v>
+        <v>327.989266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>350.2234394565609</v>
+        <v>353.2234394565609</v>
       </c>
       <c r="S40" t="n">
-        <v>3.374299374986586</v>
+        <v>6.374299374986606</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>160.9993129555745</v>
+        <v>30.92994586156361</v>
       </c>
       <c r="C41" t="n">
-        <v>128.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>78.39243392277848</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>-4.620637800094452e-11</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T41" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U41" t="n">
-        <v>328.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V41" t="n">
         <v>308.8510241668239</v>
@@ -3814,25 +3814,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H42" t="n">
-        <v>3.897332469440016</v>
+        <v>100.7619445980127</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R42" t="n">
         <v>179.532287858417</v>
@@ -3868,22 +3868,22 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T42" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>209.5483567776927</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M43" t="n">
         <v>100.6963655009106</v>
@@ -3944,7 +3944,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S43" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3978,19 +3978,19 @@
         <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>6.762021990681653</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H44" t="n">
-        <v>19.97036979779126</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T44" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U44" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V44" t="n">
         <v>308.8510241668239</v>
@@ -4038,7 +4038,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>271.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>190.3174326828064</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>194.7135206580583</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>26.93768689770263</v>
@@ -4063,13 +4063,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>18.63624233787687</v>
+        <v>192.4820063493819</v>
       </c>
       <c r="G45" t="n">
-        <v>3.986705686348098</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H45" t="n">
-        <v>3.897332469439999</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,19 +4099,19 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>500.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S45" t="n">
-        <v>452.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T45" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V45" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>111.3731429098285</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M46" t="n">
         <v>100.6963655009106</v>
@@ -4181,7 +4181,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S46" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.822852516955</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.84853105938534</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.40493940297141</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>41.99757616371015</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>37.05855726672848</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
-        <v>33.6855453124306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4324,22 +4324,22 @@
         <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>452.8308466331658</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L2" t="n">
-        <v>518.1488775879398</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="M2" t="n">
-        <v>888.4088775879397</v>
+        <v>887.2745614572864</v>
       </c>
       <c r="N2" t="n">
-        <v>1258.66887758794</v>
+        <v>1257.534561457286</v>
       </c>
       <c r="O2" t="n">
-        <v>1258.862589021146</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1318.09910993263</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.687821540228</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1220.975305607106</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>969.2704073117228</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>737.0976556280623</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>496.3163667584182</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>302.0922925557235</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.6504413609696</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="C3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="D3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="E3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="F3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="G3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="H3" t="n">
-        <v>241.4598980796927</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>174.7997405526575</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>399.7536728734559</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>716.3752280623846</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>858.5689698052438</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1049.447603846774</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.181292511625</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1350.015760438433</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1215.283546668734</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1064.436210753164</v>
+        <v>1151.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>686.6584329753858</v>
+        <v>1147.281782714996</v>
       </c>
       <c r="U3" t="n">
-        <v>308.880655197608</v>
+        <v>1147.084020807432</v>
       </c>
       <c r="V3" t="n">
-        <v>294.2234156102139</v>
+        <v>972.9377965397424</v>
       </c>
       <c r="W3" t="n">
-        <v>261.5232712568518</v>
+        <v>595.1600187619646</v>
       </c>
       <c r="X3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="Y3" t="n">
-        <v>241.4598980796927</v>
+        <v>575.0966455848054</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1250.74593757034</v>
+        <v>220.8235273665177</v>
       </c>
       <c r="C4" t="n">
-        <v>1376.747943388776</v>
+        <v>346.8255331849534</v>
       </c>
       <c r="D4" t="n">
-        <v>1379.899387017531</v>
+        <v>460.1446773099535</v>
       </c>
       <c r="E4" t="n">
-        <v>1379.899387017531</v>
+        <v>577.9735815213666</v>
       </c>
       <c r="F4" t="n">
-        <v>1379.899387017531</v>
+        <v>702.334554113302</v>
       </c>
       <c r="G4" t="n">
-        <v>1379.899387017531</v>
+        <v>855.9250003280562</v>
       </c>
       <c r="H4" t="n">
-        <v>1379.899387017531</v>
+        <v>1027.076448766142</v>
       </c>
       <c r="I4" t="n">
-        <v>1379.899387017531</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="J4" t="n">
-        <v>1379.899387017531</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="K4" t="n">
-        <v>1379.899387017531</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L4" t="n">
-        <v>1384.190642354444</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1292.035379967368</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1148.109935496879</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.0114521582486</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>664.5713836531164</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.3034377686739</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.40589968433704</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>259.2748772037976</v>
+        <v>109.0661897002255</v>
       </c>
       <c r="U4" t="n">
-        <v>505.836197055199</v>
+        <v>109.0661897002255</v>
       </c>
       <c r="V4" t="n">
-        <v>704.657589941145</v>
+        <v>109.0661897002255</v>
       </c>
       <c r="W4" t="n">
-        <v>876.5485082008224</v>
+        <v>109.0661897002255</v>
       </c>
       <c r="X4" t="n">
-        <v>1027.579299225016</v>
+        <v>109.0661897002255</v>
       </c>
       <c r="Y4" t="n">
-        <v>1138.988599904048</v>
+        <v>109.0661897002255</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.822852516955</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>56.84853105938535</v>
+        <v>56.89417848844987</v>
       </c>
       <c r="D5" t="n">
-        <v>46.40493940297142</v>
+        <v>46.45058683203594</v>
       </c>
       <c r="E5" t="n">
-        <v>41.99757616371016</v>
+        <v>42.04322359277468</v>
       </c>
       <c r="F5" t="n">
-        <v>37.05855726672849</v>
+        <v>37.10420469579301</v>
       </c>
       <c r="G5" t="n">
-        <v>33.68554531243061</v>
+        <v>33.72713203391683</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,22 +4558,22 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.35747929474751</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>83.00832592791333</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L5" t="n">
-        <v>148.3263568826872</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="M5" t="n">
-        <v>385.0262885667938</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N5" t="n">
-        <v>755.2862885667938</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
         <v>1125.74</v>
@@ -4582,28 +4582,28 @@
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1493.870580753781</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.687821540228</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1220.975305607106</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>969.2704073117228</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>737.0976556280623</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>496.3163667584183</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>302.0922925557236</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6504413609696</v>
+        <v>189.6960887900341</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1089.186506748585</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="C6" t="n">
-        <v>724.4391204399794</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="D6" t="n">
-        <v>372.9869114524009</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.7997405526575</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>399.7536728734559</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>719.1893684309202</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>861.3831101737794</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1049.447603846774</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1341.181292511625</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1496</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1359.077511216198</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1224.345297446499</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1161.305998835399</v>
+        <v>983.1551976899361</v>
       </c>
       <c r="T6" t="n">
-        <v>1156.804882835242</v>
+        <v>978.6453243046068</v>
       </c>
       <c r="U6" t="n">
-        <v>1156.6072638665</v>
+        <v>642.3174880712563</v>
       </c>
       <c r="V6" t="n">
-        <v>1141.950024279106</v>
+        <v>627.6602484838622</v>
       </c>
       <c r="W6" t="n">
-        <v>1109.249879925744</v>
+        <v>594.9601041305001</v>
       </c>
       <c r="X6" t="n">
-        <v>1089.186506748585</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="Y6" t="n">
-        <v>1089.186506748585</v>
+        <v>574.8967309533409</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259.2748772037976</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="C7" t="n">
-        <v>329.3708137314236</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="D7" t="n">
-        <v>442.6899578564237</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="E7" t="n">
-        <v>560.5188620678367</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="F7" t="n">
-        <v>684.8798346597722</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="G7" t="n">
-        <v>838.4720661204279</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="H7" t="n">
-        <v>1009.63938701753</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="I7" t="n">
-        <v>1009.63938701753</v>
+        <v>1103.17233287461</v>
       </c>
       <c r="J7" t="n">
-        <v>1379.89938701753</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1379.89938701753</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1384.190642354444</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1292.035379967367</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1148.109935496879</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.0114521582484</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>664.5713836531163</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.3034377686739</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.40589968433706</v>
+        <v>70.37478771712394</v>
       </c>
       <c r="T7" t="n">
-        <v>259.2748772037976</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U7" t="n">
-        <v>259.2748772037976</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V7" t="n">
-        <v>259.2748772037976</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="W7" t="n">
-        <v>259.2748772037976</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="X7" t="n">
-        <v>259.2748772037976</v>
+        <v>876.5096709877075</v>
       </c>
       <c r="Y7" t="n">
-        <v>259.2748772037976</v>
+        <v>876.5096709877075</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.822852516955</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>56.84853105938534</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>46.40493940297141</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>41.99757616371015</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>37.05855726672848</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>33.6855453124306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,25 +4795,25 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>452.8308466331658</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L8" t="n">
-        <v>823.0908466331658</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="M8" t="n">
-        <v>1193.350846633166</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N8" t="n">
-        <v>1436.56976765531</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1436.763479088516</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.687821540228</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1220.975305607106</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>969.2704073117228</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>737.0976556280623</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3163667584182</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>302.0922925557235</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6504413609696</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>737.7342977610062</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="C9" t="n">
-        <v>372.9869114524009</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="D9" t="n">
-        <v>372.9869114524009</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="E9" t="n">
-        <v>372.9869114524009</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.7997405526575</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>399.7536728734559</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>719.1893684309202</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>861.3831101737794</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1052.26174421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1341.181292511625</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1496</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1385.403080006397</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1250.670866236698</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>1187.631567625598</v>
+        <v>1137.041891250782</v>
       </c>
       <c r="T9" t="n">
-        <v>1183.130451625442</v>
+        <v>1132.532017865452</v>
       </c>
       <c r="U9" t="n">
-        <v>1182.932832656699</v>
+        <v>1132.334255957888</v>
       </c>
       <c r="V9" t="n">
-        <v>1168.275593069305</v>
+        <v>754.5564781801102</v>
       </c>
       <c r="W9" t="n">
-        <v>1135.575448715943</v>
+        <v>721.856333826748</v>
       </c>
       <c r="X9" t="n">
-        <v>1115.512075538784</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="Y9" t="n">
-        <v>1115.512075538784</v>
+        <v>701.7929606495888</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>774.8297405151413</v>
+        <v>849.5000447298162</v>
       </c>
       <c r="C10" t="n">
-        <v>900.8317463335771</v>
+        <v>975.502050548252</v>
       </c>
       <c r="D10" t="n">
-        <v>1014.150890458577</v>
+        <v>975.502050548252</v>
       </c>
       <c r="E10" t="n">
-        <v>1131.97979466999</v>
+        <v>975.502050548252</v>
       </c>
       <c r="F10" t="n">
-        <v>1256.340767261926</v>
+        <v>1099.863023140188</v>
       </c>
       <c r="G10" t="n">
-        <v>1384.190642354444</v>
+        <v>1099.863023140188</v>
       </c>
       <c r="H10" t="n">
-        <v>1384.190642354444</v>
+        <v>1154.778595562818</v>
       </c>
       <c r="I10" t="n">
-        <v>1384.190642354444</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="J10" t="n">
-        <v>1384.190642354444</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="K10" t="n">
-        <v>1384.190642354444</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
-        <v>1384.190642354444</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1292.035379967368</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.109935496879</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.0114521582486</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>664.5713836531164</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3034377686739</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
@@ -4986,19 +4986,19 @@
         <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>276.4812224743522</v>
       </c>
       <c r="V10" t="n">
-        <v>228.741392885946</v>
+        <v>475.3026153602981</v>
       </c>
       <c r="W10" t="n">
-        <v>400.6323111456234</v>
+        <v>475.3026153602981</v>
       </c>
       <c r="X10" t="n">
-        <v>551.6631021698169</v>
+        <v>626.3334063844917</v>
       </c>
       <c r="Y10" t="n">
-        <v>663.0724028488492</v>
+        <v>737.742707063524</v>
       </c>
     </row>
     <row r="11">
@@ -5023,7 +5023,7 @@
         <v>207.4252493128175</v>
       </c>
       <c r="G11" t="n">
-        <v>125.2531916248006</v>
+        <v>125.2531916248005</v>
       </c>
       <c r="H11" t="n">
         <v>51.92</v>
@@ -5032,31 +5032,31 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>561.4552612788618</v>
+        <v>135.4535720585666</v>
       </c>
       <c r="K11" t="n">
-        <v>1203.965261278862</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L11" t="n">
-        <v>1423.785557761274</v>
+        <v>532.4642177872098</v>
       </c>
       <c r="M11" t="n">
-        <v>1588.310595394003</v>
+        <v>999.286970190582</v>
       </c>
       <c r="N11" t="n">
-        <v>2230.820595394003</v>
+        <v>1641.796970190582</v>
       </c>
       <c r="O11" t="n">
-        <v>2395.974106525702</v>
+        <v>1806.950481322281</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2006.976374796579</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2594.597071794846</v>
       </c>
       <c r="S11" t="n">
         <v>2451.379542772653</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1011.472216904154</v>
+        <v>816.7987647058582</v>
       </c>
       <c r="C12" t="n">
-        <v>970.9672548379733</v>
+        <v>776.2938026396771</v>
       </c>
       <c r="D12" t="n">
-        <v>619.5150458503949</v>
+        <v>424.8415936520986</v>
       </c>
       <c r="E12" t="n">
-        <v>597.6240385555337</v>
+        <v>78.70816211481312</v>
       </c>
       <c r="F12" t="n">
-        <v>254.5571271031328</v>
+        <v>59.88367490483648</v>
       </c>
       <c r="G12" t="n">
-        <v>55.85669946408081</v>
+        <v>55.85669946408083</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5135,28 +5135,28 @@
         <v>2262.271670368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2080.925925057003</v>
+        <v>1886.252472858707</v>
       </c>
       <c r="S12" t="n">
-        <v>1948.016319603899</v>
+        <v>1429.100443163178</v>
       </c>
       <c r="T12" t="n">
-        <v>1865.871540558192</v>
+        <v>1346.955664117472</v>
       </c>
       <c r="U12" t="n">
-        <v>1785.911104741727</v>
+        <v>1266.995228301007</v>
       </c>
       <c r="V12" t="n">
-        <v>1691.455885356353</v>
+        <v>1172.540008915633</v>
       </c>
       <c r="W12" t="n">
-        <v>1578.957761205011</v>
+        <v>1060.041884764291</v>
       </c>
       <c r="X12" t="n">
-        <v>1479.096408229872</v>
+        <v>960.180531789152</v>
       </c>
       <c r="Y12" t="n">
-        <v>1075.670758971151</v>
+        <v>880.9973067728547</v>
       </c>
     </row>
     <row r="13">
@@ -5211,28 +5211,28 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.6348877086339</v>
+        <v>463.6348877086338</v>
       </c>
       <c r="R13" t="n">
-        <v>82.60111047978444</v>
+        <v>82.60111047978445</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
       </c>
       <c r="T13" t="n">
-        <v>153.3519263756527</v>
+        <v>164.4554332571655</v>
       </c>
       <c r="U13" t="n">
-        <v>321.7272009811524</v>
+        <v>332.8307078626652</v>
       </c>
       <c r="V13" t="n">
-        <v>442.3385938670984</v>
+        <v>453.4421007486112</v>
       </c>
       <c r="W13" t="n">
-        <v>536.0195121267758</v>
+        <v>547.1230190082886</v>
       </c>
       <c r="X13" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y13" t="n">
         <v>642.0396038300016</v>
@@ -5245,40 +5245,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.7843919601175</v>
+        <v>596.3814637549632</v>
       </c>
       <c r="C14" t="n">
-        <v>468.0120907045681</v>
+        <v>466.6091624994138</v>
       </c>
       <c r="D14" t="n">
-        <v>377.7705192501743</v>
+        <v>376.36759104502</v>
       </c>
       <c r="E14" t="n">
-        <v>293.5651762129333</v>
+        <v>292.162248007779</v>
       </c>
       <c r="F14" t="n">
-        <v>208.8281775179718</v>
+        <v>207.4252493128175</v>
       </c>
       <c r="G14" t="n">
-        <v>126.6561198299548</v>
+        <v>125.2531916248006</v>
       </c>
       <c r="H14" t="n">
-        <v>53.32292820515428</v>
+        <v>51.92</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>561.4552612788618</v>
+        <v>135.4535720585666</v>
       </c>
       <c r="K14" t="n">
-        <v>1203.965261278862</v>
+        <v>777.9635720585666</v>
       </c>
       <c r="L14" t="n">
-        <v>1423.785557761274</v>
+        <v>997.7838685409787</v>
       </c>
       <c r="M14" t="n">
-        <v>1641.796970190582</v>
+        <v>1640.293868540979</v>
       </c>
       <c r="N14" t="n">
         <v>1641.796970190582</v>
@@ -5293,28 +5293,28 @@
         <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2596</v>
+        <v>2594.597071794846</v>
       </c>
       <c r="S14" t="n">
-        <v>2452.782470977807</v>
+        <v>2451.379542772653</v>
       </c>
       <c r="T14" t="n">
-        <v>2190.644809113007</v>
+        <v>2189.241880907853</v>
       </c>
       <c r="U14" t="n">
-        <v>1859.221845744784</v>
+        <v>1857.81891753963</v>
       </c>
       <c r="V14" t="n">
-        <v>1547.251114263144</v>
+        <v>1545.84818605799</v>
       </c>
       <c r="W14" t="n">
-        <v>1226.67184559552</v>
+        <v>1225.268917390366</v>
       </c>
       <c r="X14" t="n">
-        <v>952.6497915948457</v>
+        <v>951.2468633896915</v>
       </c>
       <c r="Y14" t="n">
-        <v>760.4099606021121</v>
+        <v>759.0070323969577</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1335.714641146579</v>
+        <v>168.3139162210096</v>
       </c>
       <c r="C15" t="n">
-        <v>1100.536226882101</v>
+        <v>127.8089541548285</v>
       </c>
       <c r="D15" t="n">
-        <v>749.084017894523</v>
+        <v>100.5991694096743</v>
       </c>
       <c r="E15" t="n">
-        <v>402.9505863572374</v>
+        <v>78.70816211481309</v>
       </c>
       <c r="F15" t="n">
         <v>59.88367490483647</v>
@@ -5381,19 +5381,19 @@
         <v>1865.871540558192</v>
       </c>
       <c r="U15" t="n">
-        <v>1785.911104741727</v>
+        <v>1591.237652543431</v>
       </c>
       <c r="V15" t="n">
-        <v>1691.455885356353</v>
+        <v>1172.540008915633</v>
       </c>
       <c r="W15" t="n">
-        <v>1578.957761205011</v>
+        <v>735.7994605218668</v>
       </c>
       <c r="X15" t="n">
-        <v>1479.096408229872</v>
+        <v>311.6956833043035</v>
       </c>
       <c r="Y15" t="n">
-        <v>1399.913183213575</v>
+        <v>232.5124582880062</v>
       </c>
     </row>
     <row r="16">
@@ -5415,16 +5415,16 @@
         <v>809.2105025326554</v>
       </c>
       <c r="F16" t="n">
-        <v>844.257968243078</v>
+        <v>855.3614751245908</v>
       </c>
       <c r="G16" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1828770770499</v>
       </c>
       <c r="H16" t="n">
-        <v>1016.941316010672</v>
+        <v>1028.044822892185</v>
       </c>
       <c r="I16" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.758226418432</v>
       </c>
       <c r="J16" t="n">
         <v>1505.704370025436</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.3814637549632</v>
+        <v>597.7843919601175</v>
       </c>
       <c r="C17" t="n">
-        <v>466.6091624994138</v>
+        <v>468.0120907045681</v>
       </c>
       <c r="D17" t="n">
-        <v>376.36759104502</v>
+        <v>377.7705192501743</v>
       </c>
       <c r="E17" t="n">
-        <v>292.162248007779</v>
+        <v>293.5651762129333</v>
       </c>
       <c r="F17" t="n">
-        <v>207.4252493128175</v>
+        <v>208.8281775179718</v>
       </c>
       <c r="G17" t="n">
-        <v>125.2531916248006</v>
+        <v>126.6561198299548</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>53.32292820515431</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5509,19 +5509,19 @@
         <v>135.4535720585666</v>
       </c>
       <c r="K17" t="n">
-        <v>725.9802989115907</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L17" t="n">
-        <v>945.8005953940028</v>
+        <v>532.4642177872098</v>
       </c>
       <c r="M17" t="n">
-        <v>1588.310595394003</v>
+        <v>1145.826488868301</v>
       </c>
       <c r="N17" t="n">
-        <v>2230.820595394003</v>
+        <v>1788.336488868301</v>
       </c>
       <c r="O17" t="n">
-        <v>2395.974106525702</v>
+        <v>1953.49</v>
       </c>
       <c r="P17" t="n">
         <v>2596</v>
@@ -5530,28 +5530,28 @@
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2594.597071794846</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.379542772653</v>
+        <v>2452.782470977807</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.241880907853</v>
+        <v>2190.644809113007</v>
       </c>
       <c r="U17" t="n">
-        <v>1857.81891753963</v>
+        <v>1859.221845744784</v>
       </c>
       <c r="V17" t="n">
-        <v>1545.84818605799</v>
+        <v>1547.251114263144</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.268917390366</v>
+        <v>1226.67184559552</v>
       </c>
       <c r="X17" t="n">
-        <v>951.2468633896915</v>
+        <v>952.6497915948457</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.0070323969577</v>
+        <v>760.4099606021121</v>
       </c>
     </row>
     <row r="18">
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1011.472216904154</v>
+        <v>1335.714641146579</v>
       </c>
       <c r="C18" t="n">
-        <v>646.7248305955491</v>
+        <v>1295.209679080397</v>
       </c>
       <c r="D18" t="n">
-        <v>619.5150458503949</v>
+        <v>943.7574700928189</v>
       </c>
       <c r="E18" t="n">
-        <v>273.3816143131094</v>
+        <v>597.6240385555334</v>
       </c>
       <c r="F18" t="n">
-        <v>254.5571271031328</v>
+        <v>254.5571271031325</v>
       </c>
       <c r="G18" t="n">
-        <v>55.85669946408081</v>
+        <v>55.85669946408083</v>
       </c>
       <c r="H18" t="n">
         <v>51.92</v>
@@ -5627,10 +5627,10 @@
         <v>1578.957761205011</v>
       </c>
       <c r="X18" t="n">
-        <v>1154.853983987448</v>
+        <v>1479.096408229872</v>
       </c>
       <c r="Y18" t="n">
-        <v>1075.670758971151</v>
+        <v>1399.913183213575</v>
       </c>
     </row>
     <row r="19">
@@ -5640,28 +5640,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6904483778065</v>
+        <v>675.5869414962938</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4824541962423</v>
+        <v>723.3789473147295</v>
       </c>
       <c r="D19" t="n">
-        <v>769.5915983212424</v>
+        <v>758.4880914397296</v>
       </c>
       <c r="E19" t="n">
-        <v>809.2105025326554</v>
+        <v>798.1069956511426</v>
       </c>
       <c r="F19" t="n">
-        <v>855.3614751245908</v>
+        <v>844.257968243078</v>
       </c>
       <c r="G19" t="n">
-        <v>931.1828770770499</v>
+        <v>920.0793701955371</v>
       </c>
       <c r="H19" t="n">
-        <v>1028.044822892185</v>
+        <v>1016.941316010672</v>
       </c>
       <c r="I19" t="n">
-        <v>1189.758226418432</v>
+        <v>1178.654719536919</v>
       </c>
       <c r="J19" t="n">
         <v>1505.704370025436</v>
@@ -5685,10 +5685,10 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.6348877086339</v>
+        <v>463.6348877086338</v>
       </c>
       <c r="R19" t="n">
-        <v>82.60111047978444</v>
+        <v>82.60111047978445</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5697,19 +5697,19 @@
         <v>164.4554332571655</v>
       </c>
       <c r="U19" t="n">
-        <v>332.8307078626652</v>
+        <v>321.7272009811524</v>
       </c>
       <c r="V19" t="n">
-        <v>453.4421007486112</v>
+        <v>442.3385938670984</v>
       </c>
       <c r="W19" t="n">
-        <v>547.1230190082886</v>
+        <v>536.0195121267758</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9438100324821</v>
+        <v>608.8403031509694</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.1431107115144</v>
+        <v>642.0396038300016</v>
       </c>
     </row>
     <row r="20">
@@ -5743,31 +5743,31 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>135.4535720585666</v>
+        <v>561.4552612788618</v>
       </c>
       <c r="K20" t="n">
-        <v>312.6439213047977</v>
+        <v>738.645610525093</v>
       </c>
       <c r="L20" t="n">
-        <v>945.8005953940028</v>
+        <v>958.4659070075052</v>
       </c>
       <c r="M20" t="n">
-        <v>1588.310595394003</v>
+        <v>958.4659070075052</v>
       </c>
       <c r="N20" t="n">
-        <v>2230.820595394003</v>
+        <v>1199.31286366488</v>
       </c>
       <c r="O20" t="n">
-        <v>2395.974106525702</v>
+        <v>1364.466374796579</v>
       </c>
       <c r="P20" t="n">
-        <v>2596</v>
+        <v>2006.976374796579</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2594.597071794846</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
         <v>2451.379542772653</v>
@@ -5798,19 +5798,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1335.714641146579</v>
+        <v>1141.041188948283</v>
       </c>
       <c r="C21" t="n">
-        <v>1295.209679080397</v>
+        <v>1100.536226882101</v>
       </c>
       <c r="D21" t="n">
-        <v>943.7574700928189</v>
+        <v>749.084017894523</v>
       </c>
       <c r="E21" t="n">
-        <v>597.6240385555334</v>
+        <v>402.9505863572374</v>
       </c>
       <c r="F21" t="n">
-        <v>254.5571271031325</v>
+        <v>59.88367490483648</v>
       </c>
       <c r="G21" t="n">
         <v>55.85669946408083</v>
@@ -5943,10 +5943,10 @@
         <v>547.1230190082886</v>
       </c>
       <c r="X22" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y22" t="n">
-        <v>642.0396038300016</v>
+        <v>653.1431107115144</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.7843919601175</v>
+        <v>596.3814637549632</v>
       </c>
       <c r="C23" t="n">
-        <v>468.0120907045681</v>
+        <v>466.6091624994138</v>
       </c>
       <c r="D23" t="n">
-        <v>377.7705192501743</v>
+        <v>376.36759104502</v>
       </c>
       <c r="E23" t="n">
-        <v>293.5651762129333</v>
+        <v>292.162248007779</v>
       </c>
       <c r="F23" t="n">
-        <v>208.8281775179718</v>
+        <v>207.4252493128175</v>
       </c>
       <c r="G23" t="n">
-        <v>126.6561198299548</v>
+        <v>125.2531916248005</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5983,49 +5983,49 @@
         <v>135.4535720585666</v>
       </c>
       <c r="K23" t="n">
-        <v>777.9635720585666</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L23" t="n">
-        <v>1420.473572058567</v>
+        <v>532.4642177872098</v>
       </c>
       <c r="M23" t="n">
-        <v>2062.983572058567</v>
+        <v>1174.97421778721</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.820595394003</v>
+        <v>1817.48421778721</v>
       </c>
       <c r="O23" t="n">
-        <v>2395.974106525702</v>
+        <v>1982.637728918909</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2182.663622393207</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2594.597071794846</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.782470977807</v>
+        <v>2451.379542772653</v>
       </c>
       <c r="T23" t="n">
-        <v>2190.644809113007</v>
+        <v>2189.241880907853</v>
       </c>
       <c r="U23" t="n">
-        <v>1859.221845744784</v>
+        <v>1857.81891753963</v>
       </c>
       <c r="V23" t="n">
-        <v>1547.251114263144</v>
+        <v>1545.84818605799</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.67184559552</v>
+        <v>1225.268917390366</v>
       </c>
       <c r="X23" t="n">
-        <v>952.6497915948457</v>
+        <v>951.2468633896915</v>
       </c>
       <c r="Y23" t="n">
-        <v>760.4099606021121</v>
+        <v>759.0070323969577</v>
       </c>
     </row>
     <row r="24">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1335.714641146579</v>
+        <v>1011.472216904154</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.536226882101</v>
+        <v>776.2938026396771</v>
       </c>
       <c r="D24" t="n">
-        <v>749.084017894523</v>
+        <v>424.8415936520987</v>
       </c>
       <c r="E24" t="n">
         <v>402.9505863572374</v>
@@ -6104,7 +6104,7 @@
         <v>1479.096408229872</v>
       </c>
       <c r="Y24" t="n">
-        <v>1399.913183213575</v>
+        <v>1075.670758971151</v>
       </c>
     </row>
     <row r="25">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>601.7843919601175</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C26" t="n">
-        <v>472.0120907045681</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D26" t="n">
-        <v>381.7705192501743</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E26" t="n">
-        <v>297.5651762129333</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F26" t="n">
-        <v>212.8281775179718</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G26" t="n">
-        <v>130.6561198299548</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H26" t="n">
-        <v>57.32292820515428</v>
+        <v>52</v>
       </c>
       <c r="I26" t="n">
         <v>52</v>
@@ -6220,13 +6220,13 @@
         <v>561.5352612788618</v>
       </c>
       <c r="K26" t="n">
-        <v>1205.035261278862</v>
+        <v>738.7256105250929</v>
       </c>
       <c r="L26" t="n">
-        <v>1424.855557761274</v>
+        <v>958.545907007505</v>
       </c>
       <c r="M26" t="n">
-        <v>2068.355557761274</v>
+        <v>1602.045907007505</v>
       </c>
       <c r="N26" t="n">
         <v>2234.820595394003</v>
@@ -6241,28 +6241,28 @@
         <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2600</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S26" t="n">
-        <v>2456.782470977807</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T26" t="n">
-        <v>2194.644809113007</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U26" t="n">
-        <v>1863.221845744784</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V26" t="n">
-        <v>1551.251114263144</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W26" t="n">
-        <v>1230.67184559552</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X26" t="n">
-        <v>956.6497915948457</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y26" t="n">
-        <v>764.4099606021121</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="27">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1010.016718817569</v>
+        <v>361.5318703327206</v>
       </c>
       <c r="C27" t="n">
-        <v>969.511756751388</v>
+        <v>321.0269082665395</v>
       </c>
       <c r="D27" t="n">
-        <v>618.0595477638095</v>
+        <v>293.8171235213853</v>
       </c>
       <c r="E27" t="n">
         <v>271.926116226524</v>
@@ -6323,25 +6323,25 @@
         <v>2079.470426970418</v>
       </c>
       <c r="S27" t="n">
-        <v>1946.560821517313</v>
+        <v>1946.560821517314</v>
       </c>
       <c r="T27" t="n">
-        <v>1864.416042471606</v>
+        <v>1864.416042471607</v>
       </c>
       <c r="U27" t="n">
         <v>1784.455606655142</v>
       </c>
       <c r="V27" t="n">
-        <v>1690.000387269768</v>
+        <v>1365.757963027344</v>
       </c>
       <c r="W27" t="n">
-        <v>1253.259838876002</v>
+        <v>929.0174146335778</v>
       </c>
       <c r="X27" t="n">
-        <v>1153.398485900863</v>
+        <v>829.1560616584388</v>
       </c>
       <c r="Y27" t="n">
-        <v>1074.215260884566</v>
+        <v>425.7304123997172</v>
       </c>
     </row>
     <row r="28">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>601.7843919601175</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C29" t="n">
-        <v>472.0120907045681</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D29" t="n">
-        <v>381.7705192501743</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E29" t="n">
-        <v>297.5651762129333</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F29" t="n">
-        <v>212.8281775179718</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G29" t="n">
-        <v>130.6561198299548</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H29" t="n">
-        <v>57.32292820515428</v>
+        <v>52</v>
       </c>
       <c r="I29" t="n">
         <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>561.5352612788618</v>
+        <v>135.5335720585666</v>
       </c>
       <c r="K29" t="n">
-        <v>1205.035261278862</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L29" t="n">
-        <v>1424.855557761274</v>
+        <v>532.5442177872098</v>
       </c>
       <c r="M29" t="n">
-        <v>2068.355557761274</v>
+        <v>532.5442177872098</v>
       </c>
       <c r="N29" t="n">
-        <v>2234.820595394003</v>
+        <v>1167.450481322281</v>
       </c>
       <c r="O29" t="n">
-        <v>2399.974106525702</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P29" t="n">
-        <v>2600</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q29" t="n">
         <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2600</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S29" t="n">
-        <v>2456.782470977807</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T29" t="n">
-        <v>2194.644809113007</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U29" t="n">
-        <v>1863.221845744784</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V29" t="n">
-        <v>1551.251114263144</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W29" t="n">
-        <v>1230.67184559552</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X29" t="n">
-        <v>956.6497915948457</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y29" t="n">
-        <v>764.4099606021121</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>609.5510533860408</v>
+        <v>168.3939162210096</v>
       </c>
       <c r="C30" t="n">
-        <v>569.0460913198598</v>
+        <v>127.8889541548285</v>
       </c>
       <c r="D30" t="n">
-        <v>541.8363065747056</v>
+        <v>100.6791694096743</v>
       </c>
       <c r="E30" t="n">
-        <v>519.9452992798444</v>
+        <v>78.7881621148131</v>
       </c>
       <c r="F30" t="n">
-        <v>501.1208120698678</v>
+        <v>59.96367490483647</v>
       </c>
       <c r="G30" t="n">
-        <v>497.0938366291122</v>
+        <v>55.93669946408081</v>
       </c>
       <c r="H30" t="n">
-        <v>168.9147129226071</v>
+        <v>52</v>
       </c>
       <c r="I30" t="n">
         <v>52</v>
@@ -6554,31 +6554,31 @@
         <v>2262.351670368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2184.592931092847</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2003.247185781314</v>
+        <v>2081.005925057003</v>
       </c>
       <c r="S30" t="n">
-        <v>1870.33758032821</v>
+        <v>1948.096319603899</v>
       </c>
       <c r="T30" t="n">
-        <v>1788.192801282503</v>
+        <v>1865.951540558192</v>
       </c>
       <c r="U30" t="n">
-        <v>1708.232365466038</v>
+        <v>1591.317652543431</v>
       </c>
       <c r="V30" t="n">
-        <v>1289.53472183824</v>
+        <v>1172.620008915633</v>
       </c>
       <c r="W30" t="n">
-        <v>1177.036597686898</v>
+        <v>735.8794605218668</v>
       </c>
       <c r="X30" t="n">
-        <v>1077.175244711759</v>
+        <v>311.7756833043036</v>
       </c>
       <c r="Y30" t="n">
-        <v>997.9920196954616</v>
+        <v>232.5924582880062</v>
       </c>
     </row>
     <row r="31">
@@ -6588,28 +6588,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.7704483778067</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C31" t="n">
-        <v>734.5624541962425</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D31" t="n">
-        <v>769.6715983212425</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E31" t="n">
-        <v>809.2905025326555</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F31" t="n">
-        <v>855.441475124591</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G31" t="n">
-        <v>931.26287707705</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H31" t="n">
-        <v>1028.124822892185</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I31" t="n">
-        <v>1189.838226418432</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J31" t="n">
         <v>1505.784370025436</v>
@@ -6642,22 +6642,22 @@
         <v>52</v>
       </c>
       <c r="T31" t="n">
-        <v>164.5354332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U31" t="n">
-        <v>332.9107078626653</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V31" t="n">
-        <v>453.5221007486113</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W31" t="n">
-        <v>547.2030190082887</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X31" t="n">
-        <v>620.0238100324823</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y31" t="n">
-        <v>653.2231107115146</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="32">
@@ -6685,7 +6685,7 @@
         <v>130.6561198299548</v>
       </c>
       <c r="H32" t="n">
-        <v>57.32292820515431</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
         <v>52</v>
@@ -6694,22 +6694,22 @@
         <v>135.5335720585666</v>
       </c>
       <c r="K32" t="n">
-        <v>779.0335720585665</v>
+        <v>312.7239213047977</v>
       </c>
       <c r="L32" t="n">
-        <v>998.8538685409786</v>
+        <v>532.5442177872098</v>
       </c>
       <c r="M32" t="n">
-        <v>1591.320595394003</v>
+        <v>1176.04421778721</v>
       </c>
       <c r="N32" t="n">
-        <v>2234.820595394003</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="O32" t="n">
-        <v>2399.974106525702</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P32" t="n">
-        <v>2600</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q32" t="n">
         <v>2600</v>
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1335.794641146578</v>
+        <v>687.3097926617299</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.616226882101</v>
+        <v>646.8048305955489</v>
       </c>
       <c r="D33" t="n">
-        <v>749.1640178945229</v>
+        <v>295.3526216079704</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0305863572374</v>
+        <v>273.4616143131092</v>
       </c>
       <c r="F33" t="n">
         <v>59.96367490483648</v>
@@ -6809,13 +6809,13 @@
         <v>1691.535885356353</v>
       </c>
       <c r="W33" t="n">
-        <v>1579.037761205011</v>
+        <v>1254.795336962587</v>
       </c>
       <c r="X33" t="n">
-        <v>1479.176408229872</v>
+        <v>830.6915597450238</v>
       </c>
       <c r="Y33" t="n">
-        <v>1399.993183213575</v>
+        <v>751.5083347287265</v>
       </c>
     </row>
     <row r="34">
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>686.7704483778067</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C34" t="n">
-        <v>734.5624541962425</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D34" t="n">
         <v>758.5680914397295</v>
@@ -6891,10 +6891,10 @@
         <v>547.2030190082887</v>
       </c>
       <c r="X34" t="n">
-        <v>620.0238100324823</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y34" t="n">
-        <v>653.2231107115146</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>411.9662101420348</v>
+        <v>431.7237858995552</v>
       </c>
       <c r="C35" t="n">
-        <v>309.4666361592126</v>
+        <v>326.19390888643</v>
       </c>
       <c r="D35" t="n">
-        <v>246.4977919775462</v>
+        <v>260.1947616744605</v>
       </c>
       <c r="E35" t="n">
-        <v>189.5651762130324</v>
+        <v>200.2318428796437</v>
       </c>
       <c r="F35" t="n">
-        <v>132.1009047907982</v>
+        <v>139.7372684271064</v>
       </c>
       <c r="G35" t="n">
-        <v>89.90046435207526</v>
+        <v>93.81076738237718</v>
       </c>
       <c r="H35" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I35" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J35" t="n">
-        <v>127.3735720585686</v>
+        <v>554.2552612788627</v>
       </c>
       <c r="K35" t="n">
-        <v>304.5639213047997</v>
+        <v>731.4456105250938</v>
       </c>
       <c r="L35" t="n">
-        <v>741.7805953940854</v>
+        <v>951.2659070075059</v>
       </c>
       <c r="M35" t="n">
-        <v>1284.300595394094</v>
+        <v>1504.675907007515</v>
       </c>
       <c r="N35" t="n">
-        <v>1826.820595394102</v>
+        <v>1870.820595394047</v>
       </c>
       <c r="O35" t="n">
-        <v>1991.9741065258</v>
+        <v>2035.974106525745</v>
       </c>
       <c r="P35" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q35" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R35" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="S35" t="n">
-        <v>2076.055198250633</v>
+        <v>2117.024895220275</v>
       </c>
       <c r="T35" t="n">
-        <v>1841.190263658561</v>
+        <v>1879.129657597899</v>
       </c>
       <c r="U35" t="n">
-        <v>1537.040027563065</v>
+        <v>1571.949118472101</v>
       </c>
       <c r="V35" t="n">
-        <v>1252.342023354152</v>
+        <v>1284.220811232885</v>
       </c>
       <c r="W35" t="n">
-        <v>959.0354819592555</v>
+        <v>987.8839668076851</v>
       </c>
       <c r="X35" t="n">
-        <v>712.2861552313084</v>
+        <v>738.1043370494349</v>
       </c>
       <c r="Y35" t="n">
-        <v>547.319051511302</v>
+        <v>570.1069302991255</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1449.239938285872</v>
+        <v>753.1502413161739</v>
       </c>
       <c r="C36" t="n">
-        <v>1084.492551977267</v>
+        <v>736.8877034924171</v>
       </c>
       <c r="D36" t="n">
-        <v>733.0403429896884</v>
+        <v>733.9203429896872</v>
       </c>
       <c r="E36" t="n">
-        <v>386.9069114524029</v>
+        <v>387.7869114524018</v>
       </c>
       <c r="F36" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="G36" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="H36" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I36" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J36" t="n">
-        <v>238.2112041375651</v>
+        <v>239.091204137564</v>
       </c>
       <c r="K36" t="n">
-        <v>547.753930609307</v>
+        <v>548.6339306093059</v>
       </c>
       <c r="L36" t="n">
-        <v>980.9296988082807</v>
+        <v>981.8096988082797</v>
       </c>
       <c r="M36" t="n">
-        <v>1193.661070182701</v>
+        <v>1237.661070182646</v>
       </c>
       <c r="N36" t="n">
-        <v>1520.781953846873</v>
+        <v>1564.781953846818</v>
       </c>
       <c r="O36" t="n">
-        <v>1937.150683832479</v>
+        <v>1981.150683832424</v>
       </c>
       <c r="P36" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q36" t="n">
-        <v>2130.342422053284</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R36" t="n">
-        <v>1976.269404014479</v>
+        <v>1730.411830446087</v>
       </c>
       <c r="S36" t="n">
-        <v>1870.632525834101</v>
+        <v>1544.239798561373</v>
       </c>
       <c r="T36" t="n">
-        <v>1815.760474061122</v>
+        <v>1486.337443758091</v>
       </c>
       <c r="U36" t="n">
-        <v>1763.072765517385</v>
+        <v>1430.61943218405</v>
       </c>
       <c r="V36" t="n">
-        <v>1695.890273404738</v>
+        <v>1360.4066370411</v>
       </c>
       <c r="W36" t="n">
-        <v>1610.664876526123</v>
+        <v>1272.150937132183</v>
       </c>
       <c r="X36" t="n">
-        <v>1538.076250823712</v>
+        <v>1196.532008399468</v>
       </c>
       <c r="Y36" t="n">
-        <v>1486.165753080142</v>
+        <v>793.1063591407462</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>726.4550151206431</v>
+        <v>602.4648276393525</v>
       </c>
       <c r="C37" t="n">
-        <v>800.9770209390789</v>
+        <v>674.0168334577883</v>
       </c>
       <c r="D37" t="n">
-        <v>862.816165064079</v>
+        <v>732.8859775827883</v>
       </c>
       <c r="E37" t="n">
-        <v>929.165069275492</v>
+        <v>796.2648817942013</v>
       </c>
       <c r="F37" t="n">
-        <v>1002.046041867427</v>
+        <v>866.1758543861367</v>
       </c>
       <c r="G37" t="n">
-        <v>1002.046041867427</v>
+        <v>965.7572563385958</v>
       </c>
       <c r="H37" t="n">
-        <v>1125.637987682563</v>
+        <v>1086.379202153731</v>
       </c>
       <c r="I37" t="n">
-        <v>1314.081391208809</v>
+        <v>1271.852605679978</v>
       </c>
       <c r="J37" t="n">
-        <v>1323.341041697326</v>
+        <v>1281.112256168495</v>
       </c>
       <c r="K37" t="n">
-        <v>1402.663089148189</v>
+        <v>1409.621280269298</v>
       </c>
       <c r="L37" t="n">
-        <v>1402.663089148189</v>
+        <v>1424.755210360309</v>
       </c>
       <c r="M37" t="n">
-        <v>1328.222315914946</v>
+        <v>1347.284134096763</v>
       </c>
       <c r="N37" t="n">
-        <v>1200.341216534705</v>
+        <v>1216.372731686219</v>
       </c>
       <c r="O37" t="n">
-        <v>995.0526023797139</v>
+        <v>1008.053814500925</v>
       </c>
       <c r="P37" t="n">
-        <v>729.2814194516641</v>
+        <v>739.2523285425721</v>
       </c>
       <c r="Q37" t="n">
-        <v>401.0094331631813</v>
+        <v>407.9500392237862</v>
       </c>
       <c r="R37" t="n">
-        <v>47.24838320705913</v>
+        <v>51.15868623736106</v>
       </c>
       <c r="S37" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="T37" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="U37" t="n">
-        <v>238.9452746055017</v>
+        <v>236.8552746055006</v>
       </c>
       <c r="V37" t="n">
-        <v>386.2866674914477</v>
+        <v>381.2266674914466</v>
       </c>
       <c r="W37" t="n">
-        <v>506.6975857511251</v>
+        <v>498.667585751124</v>
       </c>
       <c r="X37" t="n">
-        <v>606.2483767753187</v>
+        <v>545.5055269603203</v>
       </c>
       <c r="Y37" t="n">
-        <v>666.1776774543509</v>
+        <v>602.4648276393525</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>424.6651001186015</v>
+        <v>431.7237858996125</v>
       </c>
       <c r="C38" t="n">
-        <v>322.1655261357794</v>
+        <v>326.1939088864873</v>
       </c>
       <c r="D38" t="n">
-        <v>259.1966819541129</v>
+        <v>260.1947616745178</v>
       </c>
       <c r="E38" t="n">
-        <v>202.2640661895992</v>
+        <v>200.231842879701</v>
       </c>
       <c r="F38" t="n">
-        <v>144.799794767365</v>
+        <v>139.7372684271637</v>
       </c>
       <c r="G38" t="n">
-        <v>89.90046435207526</v>
+        <v>81.807634981571</v>
       </c>
       <c r="H38" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I38" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J38" t="n">
-        <v>127.3735720585686</v>
+        <v>128.2535720585675</v>
       </c>
       <c r="K38" t="n">
-        <v>304.5639213047997</v>
+        <v>305.4439213047987</v>
       </c>
       <c r="L38" t="n">
-        <v>524.3842177872118</v>
+        <v>525.2642177872108</v>
       </c>
       <c r="M38" t="n">
-        <v>1066.904217787235</v>
+        <v>1078.674217787234</v>
       </c>
       <c r="N38" t="n">
-        <v>1609.424217787257</v>
+        <v>1317.410595394024</v>
       </c>
       <c r="O38" t="n">
-        <v>1774.577728918956</v>
+        <v>1482.564106525722</v>
       </c>
       <c r="P38" t="n">
-        <v>1974.603622393254</v>
+        <v>1682.590000000021</v>
       </c>
       <c r="Q38" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R38" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000101</v>
       </c>
       <c r="S38" t="n">
-        <v>2088.7540882272</v>
+        <v>2117.024895220332</v>
       </c>
       <c r="T38" t="n">
-        <v>1853.889153635127</v>
+        <v>1879.129657597956</v>
       </c>
       <c r="U38" t="n">
-        <v>1549.738917539632</v>
+        <v>1571.949118472158</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.040913330719</v>
+        <v>1284.220811232942</v>
       </c>
       <c r="W38" t="n">
-        <v>971.7343719358223</v>
+        <v>987.8839668077424</v>
       </c>
       <c r="X38" t="n">
-        <v>724.9850452078751</v>
+        <v>738.1043370494922</v>
       </c>
       <c r="Y38" t="n">
-        <v>560.0179414878687</v>
+        <v>570.1069302991827</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1510.897516232687</v>
+        <v>1179.139940475056</v>
       </c>
       <c r="C39" t="n">
-        <v>1497.665281439233</v>
+        <v>814.3925541664507</v>
       </c>
       <c r="D39" t="n">
-        <v>1146.213072451655</v>
+        <v>811.4251936637208</v>
       </c>
       <c r="E39" t="n">
-        <v>800.0796409143695</v>
+        <v>465.2917621264353</v>
       </c>
       <c r="F39" t="n">
-        <v>457.0127294619686</v>
+        <v>465.2917621264353</v>
       </c>
       <c r="G39" t="n">
-        <v>457.0127294619686</v>
+        <v>137.0223624432554</v>
       </c>
       <c r="H39" t="n">
-        <v>236.9779541117129</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I39" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J39" t="n">
-        <v>238.2112041375651</v>
+        <v>239.091204137564</v>
       </c>
       <c r="K39" t="n">
-        <v>547.753930609307</v>
+        <v>548.6339306093059</v>
       </c>
       <c r="L39" t="n">
-        <v>980.9296988082807</v>
+        <v>981.8096988082797</v>
       </c>
       <c r="M39" t="n">
-        <v>1255.85274055114</v>
+        <v>1256.732740551139</v>
       </c>
       <c r="N39" t="n">
-        <v>1582.973624215312</v>
+        <v>1583.853624215311</v>
       </c>
       <c r="O39" t="n">
-        <v>1937.150683832479</v>
+        <v>2000.222354200917</v>
       </c>
       <c r="P39" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q39" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R39" t="n">
-        <v>2037.926981961294</v>
+        <v>2078.896678930936</v>
       </c>
       <c r="S39" t="n">
-        <v>1932.290103780916</v>
+        <v>1970.229497720255</v>
       </c>
       <c r="T39" t="n">
-        <v>1877.418052007937</v>
+        <v>1912.327142916973</v>
       </c>
       <c r="U39" t="n">
-        <v>1824.7303434642</v>
+        <v>1856.609131342932</v>
       </c>
       <c r="V39" t="n">
-        <v>1757.547851351553</v>
+        <v>1786.396336199982</v>
       </c>
       <c r="W39" t="n">
-        <v>1672.322454472938</v>
+        <v>1698.140636291065</v>
       </c>
       <c r="X39" t="n">
-        <v>1599.733828770527</v>
+        <v>1622.52170755835</v>
       </c>
       <c r="Y39" t="n">
-        <v>1547.823331026957</v>
+        <v>1567.580906784477</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>865.7204483778086</v>
+        <v>845.8104483778075</v>
       </c>
       <c r="C40" t="n">
-        <v>940.2424541962444</v>
+        <v>917.3624541962432</v>
       </c>
       <c r="D40" t="n">
-        <v>1002.081598321244</v>
+        <v>976.2315983212433</v>
       </c>
       <c r="E40" t="n">
-        <v>1068.430502532658</v>
+        <v>1039.610502532656</v>
       </c>
       <c r="F40" t="n">
-        <v>1141.311475124593</v>
+        <v>1109.521475124592</v>
       </c>
       <c r="G40" t="n">
-        <v>1243.862877077052</v>
+        <v>1209.102877077051</v>
       </c>
       <c r="H40" t="n">
-        <v>1367.454822892187</v>
+        <v>1271.852605679978</v>
       </c>
       <c r="I40" t="n">
-        <v>1393.403438659672</v>
+        <v>1271.852605679978</v>
       </c>
       <c r="J40" t="n">
-        <v>1402.663089148189</v>
+        <v>1281.112256168495</v>
       </c>
       <c r="K40" t="n">
-        <v>1402.663089148189</v>
+        <v>1409.621280269298</v>
       </c>
       <c r="L40" t="n">
-        <v>1402.663089148189</v>
+        <v>1424.75521036031</v>
       </c>
       <c r="M40" t="n">
-        <v>1328.222315914946</v>
+        <v>1347.284134096764</v>
       </c>
       <c r="N40" t="n">
-        <v>1200.341216534705</v>
+        <v>1216.372731686219</v>
       </c>
       <c r="O40" t="n">
-        <v>995.0526023797139</v>
+        <v>1008.053814500925</v>
       </c>
       <c r="P40" t="n">
-        <v>729.2814194516641</v>
+        <v>739.2523285425721</v>
       </c>
       <c r="Q40" t="n">
-        <v>401.0094331631813</v>
+        <v>407.9500392237862</v>
       </c>
       <c r="R40" t="n">
-        <v>47.24838320705913</v>
+        <v>51.15868623736108</v>
       </c>
       <c r="S40" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="T40" t="n">
-        <v>183.1054332571675</v>
+        <v>181.0154332571664</v>
       </c>
       <c r="U40" t="n">
-        <v>378.2107078626672</v>
+        <v>373.1507078626661</v>
       </c>
       <c r="V40" t="n">
-        <v>525.5521007486132</v>
+        <v>517.522100748612</v>
       </c>
       <c r="W40" t="n">
-        <v>645.9630190082905</v>
+        <v>634.9630190082895</v>
       </c>
       <c r="X40" t="n">
-        <v>745.5138100324841</v>
+        <v>731.5438100324831</v>
       </c>
       <c r="Y40" t="n">
-        <v>805.4431107115164</v>
+        <v>788.5031107115153</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>337.0019209824677</v>
+        <v>369.1675910450209</v>
       </c>
       <c r="C41" t="n">
-        <v>207.2296197269183</v>
+        <v>369.1675910450209</v>
       </c>
       <c r="D41" t="n">
-        <v>207.2296197269183</v>
+        <v>369.1675910450209</v>
       </c>
       <c r="E41" t="n">
-        <v>123.0242766896772</v>
+        <v>284.9622480077799</v>
       </c>
       <c r="F41" t="n">
-        <v>43.84000000000197</v>
+        <v>200.2252493128184</v>
       </c>
       <c r="G41" t="n">
-        <v>43.84000000000197</v>
+        <v>118.0531916248014</v>
       </c>
       <c r="H41" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I41" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J41" t="n">
-        <v>553.3752612788638</v>
+        <v>554.2552612788627</v>
       </c>
       <c r="K41" t="n">
-        <v>1095.895261278888</v>
+        <v>731.4456105250938</v>
       </c>
       <c r="L41" t="n">
-        <v>1315.7155577613</v>
+        <v>951.2659070075059</v>
       </c>
       <c r="M41" t="n">
-        <v>1826.820595394102</v>
+        <v>1504.675907007544</v>
       </c>
       <c r="N41" t="n">
-        <v>1826.820595394102</v>
+        <v>1870.820595394047</v>
       </c>
       <c r="O41" t="n">
-        <v>1991.9741065258</v>
+        <v>2035.974106525745</v>
       </c>
       <c r="P41" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q41" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R41" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="S41" t="n">
-        <v>2192.000000000157</v>
+        <v>2092.782470977851</v>
       </c>
       <c r="T41" t="n">
-        <v>1929.862338135357</v>
+        <v>1830.644809113051</v>
       </c>
       <c r="U41" t="n">
-        <v>1598.439374767134</v>
+        <v>1499.221845744828</v>
       </c>
       <c r="V41" t="n">
-        <v>1286.468643285494</v>
+        <v>1187.251114263188</v>
       </c>
       <c r="W41" t="n">
-        <v>965.8893746178703</v>
+        <v>866.671845595564</v>
       </c>
       <c r="X41" t="n">
-        <v>691.8673206171959</v>
+        <v>592.6497915948896</v>
       </c>
       <c r="Y41" t="n">
-        <v>499.6274896244622</v>
+        <v>400.4099606021559</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>808.7187647058601</v>
+        <v>583.1993830175486</v>
       </c>
       <c r="C42" t="n">
-        <v>768.213802639679</v>
+        <v>218.4519967089432</v>
       </c>
       <c r="D42" t="n">
-        <v>416.7615936521006</v>
+        <v>191.2422119637891</v>
       </c>
       <c r="E42" t="n">
-        <v>70.6281621148151</v>
+        <v>169.3512046689278</v>
       </c>
       <c r="F42" t="n">
-        <v>51.80367490483846</v>
+        <v>150.5267174589512</v>
       </c>
       <c r="G42" t="n">
-        <v>47.7766994640828</v>
+        <v>146.4997420181955</v>
       </c>
       <c r="H42" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I42" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J42" t="n">
-        <v>238.2112041375651</v>
+        <v>239.091204137564</v>
       </c>
       <c r="K42" t="n">
-        <v>547.753930609307</v>
+        <v>548.6339306093059</v>
       </c>
       <c r="L42" t="n">
-        <v>918.7380284398416</v>
+        <v>962.7380284397866</v>
       </c>
       <c r="M42" t="n">
-        <v>1193.661070182701</v>
+        <v>1237.661070182646</v>
       </c>
       <c r="N42" t="n">
-        <v>1520.781953846873</v>
+        <v>1564.781953846818</v>
       </c>
       <c r="O42" t="n">
-        <v>1937.150683832479</v>
+        <v>1981.150683832424</v>
       </c>
       <c r="P42" t="n">
-        <v>2192.000000000099</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q42" t="n">
-        <v>2192.000000000099</v>
+        <v>2158.241260724355</v>
       </c>
       <c r="R42" t="n">
-        <v>2010.654254688566</v>
+        <v>1976.895515412822</v>
       </c>
       <c r="S42" t="n">
-        <v>1877.744649235462</v>
+        <v>1843.985909959717</v>
       </c>
       <c r="T42" t="n">
-        <v>1795.599870189755</v>
+        <v>1761.841130914011</v>
       </c>
       <c r="U42" t="n">
-        <v>1715.63943437329</v>
+        <v>1681.880695097546</v>
       </c>
       <c r="V42" t="n">
-        <v>1621.184214987916</v>
+        <v>1587.425475712172</v>
       </c>
       <c r="W42" t="n">
-        <v>1508.686090836574</v>
+        <v>1150.684927318406</v>
       </c>
       <c r="X42" t="n">
-        <v>1408.824737861435</v>
+        <v>1050.823574343267</v>
       </c>
       <c r="Y42" t="n">
-        <v>1197.159731015281</v>
+        <v>647.3979250845451</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>678.6104483778087</v>
+        <v>668.3869414962949</v>
       </c>
       <c r="C43" t="n">
-        <v>726.4024541962444</v>
+        <v>716.1789473147306</v>
       </c>
       <c r="D43" t="n">
-        <v>761.5115983212445</v>
+        <v>751.2880914397307</v>
       </c>
       <c r="E43" t="n">
-        <v>801.1305025326575</v>
+        <v>790.9069956511437</v>
       </c>
       <c r="F43" t="n">
-        <v>847.2814751245929</v>
+        <v>837.0579682430791</v>
       </c>
       <c r="G43" t="n">
-        <v>923.102877077052</v>
+        <v>912.8793701955382</v>
       </c>
       <c r="H43" t="n">
-        <v>1019.964822892187</v>
+        <v>1009.741316010673</v>
       </c>
       <c r="I43" t="n">
-        <v>1181.678226418434</v>
+        <v>1171.45471953692</v>
       </c>
       <c r="J43" t="n">
-        <v>1508.727876906951</v>
+        <v>1498.504370025437</v>
       </c>
       <c r="K43" t="n">
-        <v>1602.373394126241</v>
+        <v>1603.25339412624</v>
       </c>
       <c r="L43" t="n">
-        <v>1593.57218005728</v>
+        <v>1594.452180057279</v>
       </c>
       <c r="M43" t="n">
-        <v>1491.85867955131</v>
+        <v>1492.738679551309</v>
       </c>
       <c r="N43" t="n">
-        <v>1336.704852898341</v>
+        <v>1337.58485289834</v>
       </c>
       <c r="O43" t="n">
-        <v>1104.143511470623</v>
+        <v>1105.023511470622</v>
       </c>
       <c r="P43" t="n">
-        <v>811.0996012698458</v>
+        <v>811.9796012698448</v>
       </c>
       <c r="Q43" t="n">
-        <v>455.5548877086358</v>
+        <v>456.4348877086347</v>
       </c>
       <c r="R43" t="n">
-        <v>74.52111047978642</v>
+        <v>75.4011104797853</v>
       </c>
       <c r="S43" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="T43" t="n">
-        <v>156.3754332571675</v>
+        <v>146.1519263756537</v>
       </c>
       <c r="U43" t="n">
-        <v>324.7507078626672</v>
+        <v>314.5272009811535</v>
       </c>
       <c r="V43" t="n">
-        <v>445.3621007486132</v>
+        <v>435.1385938670995</v>
       </c>
       <c r="W43" t="n">
-        <v>539.0430190082907</v>
+        <v>528.8195121267769</v>
       </c>
       <c r="X43" t="n">
-        <v>611.8638100324843</v>
+        <v>601.6403031509705</v>
       </c>
       <c r="Y43" t="n">
-        <v>645.0631107115165</v>
+        <v>634.8396038300027</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>193.784391960391</v>
+        <v>511.8064459608358</v>
       </c>
       <c r="C44" t="n">
-        <v>64.01209070484163</v>
+        <v>382.0341447052864</v>
       </c>
       <c r="D44" t="n">
-        <v>64.01209070484163</v>
+        <v>291.7925732508926</v>
       </c>
       <c r="E44" t="n">
-        <v>64.01209070484163</v>
+        <v>284.9622480077799</v>
       </c>
       <c r="F44" t="n">
-        <v>64.01209070484163</v>
+        <v>200.2252493128184</v>
       </c>
       <c r="G44" t="n">
-        <v>64.01209070484163</v>
+        <v>118.0531916248014</v>
       </c>
       <c r="H44" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I44" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J44" t="n">
-        <v>127.3735720585686</v>
+        <v>554.2552612788627</v>
       </c>
       <c r="K44" t="n">
-        <v>669.893572058593</v>
+        <v>731.4456105250938</v>
       </c>
       <c r="L44" t="n">
-        <v>889.7138685410051</v>
+        <v>951.2659070075059</v>
       </c>
       <c r="M44" t="n">
-        <v>1432.233868541071</v>
+        <v>951.2659070075059</v>
       </c>
       <c r="N44" t="n">
-        <v>1826.820595394276</v>
+        <v>1482.564106525679</v>
       </c>
       <c r="O44" t="n">
-        <v>1991.974106525975</v>
+        <v>2035.974106525745</v>
       </c>
       <c r="P44" t="n">
-        <v>2192.000000000273</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q44" t="n">
-        <v>2192.000000000273</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R44" t="n">
-        <v>2192.000000000273</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="S44" t="n">
-        <v>2048.78247097808</v>
+        <v>2092.782470977851</v>
       </c>
       <c r="T44" t="n">
-        <v>1786.64480911328</v>
+        <v>1830.644809113051</v>
       </c>
       <c r="U44" t="n">
-        <v>1455.221845745058</v>
+        <v>1499.221845744828</v>
       </c>
       <c r="V44" t="n">
-        <v>1143.251114263418</v>
+        <v>1187.251114263188</v>
       </c>
       <c r="W44" t="n">
-        <v>822.6718455957937</v>
+        <v>866.671845595564</v>
       </c>
       <c r="X44" t="n">
-        <v>548.6497915951193</v>
+        <v>866.671845595564</v>
       </c>
       <c r="Y44" t="n">
-        <v>356.4099606023855</v>
+        <v>674.4320146028303</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>484.4763404634359</v>
+        <v>985.2005465356621</v>
       </c>
       <c r="C45" t="n">
-        <v>119.7289541548305</v>
+        <v>944.695584469481</v>
       </c>
       <c r="D45" t="n">
-        <v>92.51916940967631</v>
+        <v>917.4857997243269</v>
       </c>
       <c r="E45" t="n">
-        <v>70.62816211481507</v>
+        <v>895.5947924294657</v>
       </c>
       <c r="F45" t="n">
-        <v>51.80367490483844</v>
+        <v>701.1685233896859</v>
       </c>
       <c r="G45" t="n">
-        <v>47.77669946408278</v>
+        <v>372.899123706506</v>
       </c>
       <c r="H45" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="I45" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="J45" t="n">
-        <v>238.2112041375651</v>
+        <v>239.091204137564</v>
       </c>
       <c r="K45" t="n">
-        <v>547.753930609307</v>
+        <v>548.6339306093059</v>
       </c>
       <c r="L45" t="n">
-        <v>980.9296988082807</v>
+        <v>962.7380284397866</v>
       </c>
       <c r="M45" t="n">
-        <v>1255.85274055114</v>
+        <v>1237.661070182646</v>
       </c>
       <c r="N45" t="n">
-        <v>1520.781953847048</v>
+        <v>1564.781953846818</v>
       </c>
       <c r="O45" t="n">
-        <v>1937.150683832653</v>
+        <v>1981.150683832424</v>
       </c>
       <c r="P45" t="n">
-        <v>2192.000000000273</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q45" t="n">
-        <v>2192.000000000273</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="R45" t="n">
-        <v>1686.411830446317</v>
+        <v>2054.654254688511</v>
       </c>
       <c r="S45" t="n">
-        <v>1229.259800750788</v>
+        <v>1921.744649235407</v>
       </c>
       <c r="T45" t="n">
-        <v>1147.115021705081</v>
+        <v>1839.5998701897</v>
       </c>
       <c r="U45" t="n">
-        <v>1067.154585888617</v>
+        <v>1759.639434373235</v>
       </c>
       <c r="V45" t="n">
-        <v>972.6993665032427</v>
+        <v>1340.941790745437</v>
       </c>
       <c r="W45" t="n">
-        <v>860.2012423519008</v>
+        <v>1228.443666594095</v>
       </c>
       <c r="X45" t="n">
-        <v>760.3398893767618</v>
+        <v>1128.582313618956</v>
       </c>
       <c r="Y45" t="n">
-        <v>681.1566643604644</v>
+        <v>1049.399088602659</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>667.5069414962957</v>
+        <v>668.3869414962949</v>
       </c>
       <c r="C46" t="n">
-        <v>715.2989473147314</v>
+        <v>716.1789473147306</v>
       </c>
       <c r="D46" t="n">
-        <v>750.4080914397315</v>
+        <v>751.2880914397307</v>
       </c>
       <c r="E46" t="n">
-        <v>790.0269956511445</v>
+        <v>790.9069956511437</v>
       </c>
       <c r="F46" t="n">
-        <v>836.1779682430799</v>
+        <v>837.0579682430791</v>
       </c>
       <c r="G46" t="n">
-        <v>911.999370195539</v>
+        <v>912.8793701955382</v>
       </c>
       <c r="H46" t="n">
-        <v>1008.861316010674</v>
+        <v>1009.741316010673</v>
       </c>
       <c r="I46" t="n">
-        <v>1170.574719536921</v>
+        <v>1171.45471953692</v>
       </c>
       <c r="J46" t="n">
-        <v>1497.624370025438</v>
+        <v>1498.504370025437</v>
       </c>
       <c r="K46" t="n">
-        <v>1602.373394126241</v>
+        <v>1603.25339412624</v>
       </c>
       <c r="L46" t="n">
-        <v>1593.57218005728</v>
+        <v>1594.45218005728</v>
       </c>
       <c r="M46" t="n">
-        <v>1491.85867955131</v>
+        <v>1492.738679551309</v>
       </c>
       <c r="N46" t="n">
-        <v>1336.704852898341</v>
+        <v>1337.58485289834</v>
       </c>
       <c r="O46" t="n">
-        <v>1104.143511470623</v>
+        <v>1105.023511470622</v>
       </c>
       <c r="P46" t="n">
-        <v>811.0996012698458</v>
+        <v>811.9796012698448</v>
       </c>
       <c r="Q46" t="n">
-        <v>455.5548877086358</v>
+        <v>456.4348877086347</v>
       </c>
       <c r="R46" t="n">
-        <v>74.5211104797864</v>
+        <v>75.40111047978533</v>
       </c>
       <c r="S46" t="n">
-        <v>43.84000000000197</v>
+        <v>44.72000000000087</v>
       </c>
       <c r="T46" t="n">
-        <v>145.2719263756545</v>
+        <v>146.1519263756537</v>
       </c>
       <c r="U46" t="n">
-        <v>313.6472009811543</v>
+        <v>314.5272009811535</v>
       </c>
       <c r="V46" t="n">
-        <v>434.2585938671003</v>
+        <v>435.1385938670995</v>
       </c>
       <c r="W46" t="n">
-        <v>527.9395121267777</v>
+        <v>528.8195121267769</v>
       </c>
       <c r="X46" t="n">
-        <v>600.7603031509713</v>
+        <v>601.6403031509705</v>
       </c>
       <c r="Y46" t="n">
-        <v>633.9596038300035</v>
+        <v>634.8396038300027</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>373.5581017224773</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>844.8491025166892</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>776.6480334467196</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>182.0990798101954</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>307.3714877557712</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>385.2467704309743</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="M5" t="n">
-        <v>709.9399426016454</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>776.6480334467196</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
-        <v>314.1651303924402</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>501.6736190008522</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8292,7 +8292,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N6" t="n">
-        <v>482.5659611425265</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O6" t="n">
         <v>382.6817988009037</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>373.5581017224773</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>308.0221909547738</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="M8" t="n">
-        <v>844.8491025166892</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>648.3237112468647</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>127.6736190008522</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8532,7 +8532,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
-        <v>379.8392327720798</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
         <v>219.1507118405495</v>
@@ -8675,16 +8675,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>470.019849246231</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>463.3859690154104</v>
+        <v>768.7371960564642</v>
       </c>
       <c r="N11" t="n">
         <v>875.1881540497347</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>470.019849246231</v>
+        <v>470.0198492462312</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>517.4126102240763</v>
+        <v>946.1990623156843</v>
       </c>
       <c r="N14" t="n">
-        <v>226.1881540497347</v>
+        <v>227.7064385442836</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9152,13 +9152,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>417.5114925321142</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>946.1990623156843</v>
+        <v>916.7569118925443</v>
       </c>
       <c r="N17" t="n">
         <v>875.1881540497347</v>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>446.9536429552543</v>
       </c>
       <c r="Q17" t="n">
         <v>20.87871447823917</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>417.5114925321142</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>946.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N20" t="n">
-        <v>875.1881540497347</v>
+        <v>469.4679082491035</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>446.9536429552543</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>470.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>426.9592964824121</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>946.1990623156843</v>
       </c>
       <c r="N23" t="n">
-        <v>395.7205008532052</v>
+        <v>875.1881540497347</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.87871447823917</v>
+        <v>438.3902070103535</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>471.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
         <v>947.1990623156843</v>
       </c>
       <c r="N26" t="n">
-        <v>394.334656709057</v>
+        <v>865.354505955288</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>471.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>947.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N29" t="n">
-        <v>394.334656709057</v>
+        <v>867.507612165968</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>483.1782715841426</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>471.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>895.650301561163</v>
+        <v>947.1990623156843</v>
       </c>
       <c r="N32" t="n">
-        <v>876.1881540497347</v>
+        <v>700.6858837501106</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>219.5923006130035</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>845.1990623156925</v>
+        <v>856.1990623156929</v>
       </c>
       <c r="N35" t="n">
-        <v>774.1881540497429</v>
+        <v>596.0312736320905</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10659,7 +10659,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M36" t="n">
-        <v>408.874951371078</v>
+        <v>452.430506926579</v>
       </c>
       <c r="N36" t="n">
         <v>485.4085271713503</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>845.199062315707</v>
+        <v>856.1990623157075</v>
       </c>
       <c r="N38" t="n">
-        <v>774.1881540497575</v>
+        <v>467.3360102182093</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>240.4710150912136</v>
+        <v>579.8787144782625</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10902,10 +10902,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>319.8619297418743</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>199.8863983370213</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11048,16 +11048,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>369.0198492462559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>813.4667770962917</v>
+        <v>856.199062315722</v>
       </c>
       <c r="N41" t="n">
-        <v>226.1881540497347</v>
+        <v>596.031273632061</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>325.2694674007688</v>
+        <v>368.8250229562698</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>369.0198492462558</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>845.1990623157507</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N44" t="n">
-        <v>624.7606054166089</v>
+        <v>762.8530020478895</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>392.1782715842097</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -11367,13 +11367,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>368.8250229562698</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>422.5886581124973</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
         <v>382.6817988009037</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>12.57190107680112</v>
+        <v>11.88310107685484</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>11.88310107679809</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>12.57190107680108</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>130.0693670940109</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>89.33915573984979</v>
@@ -25605,13 +25605,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>5.497194785233361</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>81.35033711113681</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>72.59985970855251</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>141.7853537320288</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25836,19 +25836,19 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>89.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>83.36328960686865</v>
+        <v>76.60126761618699</v>
       </c>
       <c r="F44" t="n">
-        <v>83.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>81.35033711113681</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>52.62948991076129</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>979419.8932442359</v>
+        <v>979565.8926841225</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1860983.821477052</v>
+        <v>1861129.820916938</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742547.749709869</v>
+        <v>2742693.749149755</v>
       </c>
     </row>
     <row r="5">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10664591.15054631</v>
+        <v>10666223.66381563</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11545454.57245113</v>
+        <v>11547125.46565646</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12405255.83435595</v>
+        <v>12409305.34749728</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13265057.09626079</v>
+        <v>13271485.2293381</v>
       </c>
     </row>
   </sheetData>
@@ -26272,19 +26272,19 @@
         <v>1322345.892349224</v>
       </c>
       <c r="C2" t="n">
-        <v>1322345.892349223</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="D2" t="n">
         <v>1322345.892349224</v>
       </c>
       <c r="E2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="F2" t="n">
         <v>1322345.892349225</v>
       </c>
       <c r="G2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="H2" t="n">
         <v>1322345.892349224</v>
@@ -26296,22 +26296,22 @@
         <v>1322345.892349225</v>
       </c>
       <c r="K2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="L2" t="n">
         <v>1322345.892349224</v>
       </c>
       <c r="M2" t="n">
-        <v>1321295.132857224</v>
+        <v>1321352.70276122</v>
       </c>
       <c r="N2" t="n">
-        <v>1321295.132857225</v>
+        <v>1321352.702761226</v>
       </c>
       <c r="O2" t="n">
-        <v>1289701.892857225</v>
+        <v>1293269.822761221</v>
       </c>
       <c r="P2" t="n">
-        <v>1289701.892857241</v>
+        <v>1293269.82276122</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>233048</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>593450</v>
+        <v>594425</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26354,13 +26354,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>82496.00000000869</v>
+        <v>83968.00000000384</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>235200</v>
+        <v>237600</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>601944.7387873891</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>599936.661423816</v>
+        <v>599959.4017938485</v>
       </c>
       <c r="D4" t="n">
-        <v>597925.8599779638</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>513253.1653847605</v>
+        <v>513056.3660364838</v>
       </c>
       <c r="F4" t="n">
-        <v>511570.4197316588</v>
+        <v>511373.620383382</v>
       </c>
       <c r="G4" t="n">
-        <v>509885.3519526902</v>
+        <v>509688.5526044134</v>
       </c>
       <c r="H4" t="n">
-        <v>508197.9453958013</v>
+        <v>508001.1460475244</v>
       </c>
       <c r="I4" t="n">
-        <v>506508.1831919707</v>
+        <v>506311.3838436939</v>
       </c>
       <c r="J4" t="n">
-        <v>504742.7776510159</v>
+        <v>504545.7862134473</v>
       </c>
       <c r="K4" t="n">
-        <v>503048.9703867822</v>
+        <v>502851.9789492135</v>
       </c>
       <c r="L4" t="n">
-        <v>501352.7565448462</v>
+        <v>501155.7651072776</v>
       </c>
       <c r="M4" t="n">
-        <v>506900.8702293737</v>
+        <v>505559.3102707667</v>
       </c>
       <c r="N4" t="n">
-        <v>505122.7353936197</v>
+        <v>503793.1759878677</v>
       </c>
       <c r="O4" t="n">
-        <v>487069.0669492238</v>
+        <v>487559.9239341616</v>
       </c>
       <c r="P4" t="n">
-        <v>485355.9559140749</v>
+        <v>485851.0486089999</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58634</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58634</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58634</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>74075.349</v>
@@ -26458,16 +26458,16 @@
         <v>74136.149</v>
       </c>
       <c r="M5" t="n">
-        <v>70204.4120000015</v>
+        <v>70621.00500000066</v>
       </c>
       <c r="N5" t="n">
-        <v>70204.4120000015</v>
+        <v>70621.00500000066</v>
       </c>
       <c r="O5" t="n">
-        <v>67934.54900000151</v>
+        <v>68603.34900000066</v>
       </c>
       <c r="P5" t="n">
-        <v>67934.54900000151</v>
+        <v>68603.34900000066</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>428719.1535618347</v>
+        <v>429692.9264977697</v>
       </c>
       <c r="C6" t="n">
-        <v>663775.2309254071</v>
+        <v>663774.2905553754</v>
       </c>
       <c r="D6" t="n">
-        <v>665786.0323712605</v>
+        <v>665785.3790841795</v>
       </c>
       <c r="E6" t="n">
-        <v>141567.377964464</v>
+        <v>140789.1773127403</v>
       </c>
       <c r="F6" t="n">
-        <v>736700.1236175657</v>
+        <v>736896.922965843</v>
       </c>
       <c r="G6" t="n">
-        <v>738385.1913965348</v>
+        <v>738581.9907448107</v>
       </c>
       <c r="H6" t="n">
-        <v>740072.5979534228</v>
+        <v>740269.3973016998</v>
       </c>
       <c r="I6" t="n">
-        <v>741762.3601572536</v>
+        <v>741959.1595055301</v>
       </c>
       <c r="J6" t="n">
-        <v>354666.9656982089</v>
+        <v>354863.9571357779</v>
       </c>
       <c r="K6" t="n">
-        <v>745160.7729624421</v>
+        <v>745357.764400011</v>
       </c>
       <c r="L6" t="n">
-        <v>746856.9868043781</v>
+        <v>747053.9782419465</v>
       </c>
       <c r="M6" t="n">
-        <v>661693.8506278404</v>
+        <v>661204.3874904487</v>
       </c>
       <c r="N6" t="n">
-        <v>745967.9854636034</v>
+        <v>746938.521773358</v>
       </c>
       <c r="O6" t="n">
-        <v>499498.2769079995</v>
+        <v>499506.5498270583</v>
       </c>
       <c r="P6" t="n">
-        <v>736411.3879431641</v>
+        <v>738815.4251522198</v>
       </c>
     </row>
   </sheetData>
@@ -26788,10 +26788,10 @@
         <v>321</v>
       </c>
       <c r="M2" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N2" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>350</v>
@@ -26892,16 +26892,16 @@
         <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>548.0000000000247</v>
+        <v>559.0000000000109</v>
       </c>
       <c r="N4" t="n">
-        <v>548.0000000000247</v>
+        <v>559.0000000000109</v>
       </c>
       <c r="O4" t="n">
-        <v>548.0000000000247</v>
+        <v>559.0000000000109</v>
       </c>
       <c r="P4" t="n">
-        <v>548.0000000000247</v>
+        <v>559.0000000000109</v>
       </c>
     </row>
   </sheetData>
@@ -26984,10 +26984,10 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27005,13 +27005,13 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27094,7 +27094,7 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -27103,13 +27103,13 @@
         <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>173.0000000000176</v>
+        <v>184.0000000000038</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>133.9627275218806</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.6157244564351</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>397.8918749462437</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5158377618198</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0076343562325</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27563,19 +27563,19 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>313.0700430685739</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>30.45610484015533</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.19564277905467</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>242.1059051665076</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27597,31 +27597,31 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>288.7194944482368</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8563318579235</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.103716265553</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>170.9935867676593</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.00980129492416</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>266.7319213421267</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,22 +27645,22 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>248.3131841742358</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>133.9627275218806</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>222.5075994026788</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27752,25 +27752,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5158377618198</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0076343562325</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4244990988957</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,19 +27794,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.971133269987064</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>88.44885845517734</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>67.2312264174717</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27831,31 +27831,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>343.5292229385759</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H7" t="n">
+        <v>227.1197490524383</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="J7" t="n">
+        <v>170.158444430092</v>
+      </c>
+      <c r="K7" t="n">
         <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>400</v>
-      </c>
-      <c r="H7" t="n">
-        <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>170.9935867676593</v>
-      </c>
-      <c r="J7" t="n">
-        <v>396.0098012949242</v>
-      </c>
-      <c r="K7" t="n">
-        <v>266.7319213421267</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27885,13 +27885,13 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9481617662612</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>133.9627275218806</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.6157244564351</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>397.8918749462437</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28001,13 +28001,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5158377618198</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0076343562325</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4244990988957</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.03344637228429</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>240.7966850804141</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28046,7 +28046,7 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28071,31 +28071,31 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>373.9976198301641</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>227.103716265553</v>
+        <v>282.5900242268127</v>
       </c>
       <c r="I10" t="n">
-        <v>170.9935867676593</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>22.00980129492416</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>266.7319213421267</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>395.6653986495825</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.105151834003</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2232550308479</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9481617662612</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28192,10 +28192,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>162.4939254614603</v>
+        <v>161.1050265383575</v>
       </c>
       <c r="S11" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="T11" t="n">
         <v>321</v>
@@ -28232,13 +28232,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>128.2732823236866</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28271,10 +28271,10 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>128.2732823236866</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28292,7 +28292,7 @@
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28356,7 +28356,7 @@
         <v>321</v>
       </c>
       <c r="T13" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="U13" t="n">
         <v>321</v>
@@ -28371,7 +28371,7 @@
         <v>321</v>
       </c>
       <c r="Y13" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
     </row>
     <row r="14">
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>94.44753714149141</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>162.4939254614603</v>
+        <v>161.1050265383575</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28463,16 +28463,16 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28517,16 +28517,16 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>321</v>
@@ -28551,7 +28551,7 @@
         <v>321</v>
       </c>
       <c r="F16" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
       <c r="G16" t="n">
         <v>321</v>
@@ -28563,7 +28563,7 @@
         <v>321</v>
       </c>
       <c r="J16" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="K16" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>95.83643606459415</v>
+        <v>94.44753714149138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28700,19 +28700,19 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>128.2732823236866</v>
+        <v>128.273282323687</v>
       </c>
       <c r="H18" t="n">
         <v>321</v>
@@ -28763,7 +28763,7 @@
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28800,7 +28800,7 @@
         <v>321</v>
       </c>
       <c r="J19" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="K19" t="n">
         <v>321</v>
@@ -28833,7 +28833,7 @@
         <v>321</v>
       </c>
       <c r="U19" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="V19" t="n">
         <v>321</v>
@@ -28903,10 +28903,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S20" t="n">
-        <v>321</v>
+        <v>319.6111010768973</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="C21" t="n">
         <v>321</v>
@@ -28949,7 +28949,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>128.273282323687</v>
+        <v>321</v>
       </c>
       <c r="H21" t="n">
         <v>321</v>
@@ -29013,7 +29013,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="C22" t="n">
         <v>321</v>
@@ -29079,7 +29079,7 @@
         <v>321</v>
       </c>
       <c r="X22" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="Y22" t="n">
         <v>321</v>
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>319.6111010768972</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>95.83643606459415</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>162.4939254614603</v>
+        <v>161.1050265383575</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29174,13 +29174,13 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>128.2732823236869</v>
+        <v>128.2732823236868</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -29240,7 +29240,7 @@
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>90.56673714149142</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>162.4939254614603</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29414,10 +29414,10 @@
         <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29456,7 +29456,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R27" t="n">
-        <v>319.4798568942803</v>
+        <v>319.4798568942807</v>
       </c>
       <c r="S27" t="n">
         <v>321</v>
@@ -29468,7 +29468,7 @@
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -29477,7 +29477,7 @@
         <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>90.56673714149142</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>162.4939254614603</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
@@ -29663,10 +29663,10 @@
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>75.46100877721284</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29702,16 +29702,16 @@
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>321</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29748,37 +29748,37 @@
         <v>321</v>
       </c>
       <c r="J31" t="n">
+        <v>321</v>
+      </c>
+      <c r="K31" t="n">
+        <v>321</v>
+      </c>
+      <c r="L31" t="n">
+        <v>321</v>
+      </c>
+      <c r="M31" t="n">
+        <v>321</v>
+      </c>
+      <c r="N31" t="n">
+        <v>321</v>
+      </c>
+      <c r="O31" t="n">
+        <v>321</v>
+      </c>
+      <c r="P31" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>321</v>
+      </c>
+      <c r="R31" t="n">
+        <v>321</v>
+      </c>
+      <c r="S31" t="n">
+        <v>321</v>
+      </c>
+      <c r="T31" t="n">
         <v>309.7843364833203</v>
-      </c>
-      <c r="K31" t="n">
-        <v>321</v>
-      </c>
-      <c r="L31" t="n">
-        <v>321</v>
-      </c>
-      <c r="M31" t="n">
-        <v>321</v>
-      </c>
-      <c r="N31" t="n">
-        <v>321</v>
-      </c>
-      <c r="O31" t="n">
-        <v>321</v>
-      </c>
-      <c r="P31" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>321</v>
-      </c>
-      <c r="R31" t="n">
-        <v>321</v>
-      </c>
-      <c r="S31" t="n">
-        <v>321</v>
-      </c>
-      <c r="T31" t="n">
-        <v>321</v>
       </c>
       <c r="U31" t="n">
         <v>321</v>
@@ -29821,10 +29821,10 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>315.7303010768973</v>
       </c>
       <c r="I32" t="n">
-        <v>90.56673714149139</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29885,16 +29885,16 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
+        <v>321</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>321</v>
+      </c>
+      <c r="F33" t="n">
         <v>128.2732823236869</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29945,10 +29945,10 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -29967,7 +29967,7 @@
         <v>321</v>
       </c>
       <c r="D34" t="n">
-        <v>309.7843364833202</v>
+        <v>321</v>
       </c>
       <c r="E34" t="n">
         <v>321</v>
@@ -30027,7 +30027,7 @@
         <v>321</v>
       </c>
       <c r="X34" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="Y34" t="n">
         <v>321</v>
@@ -30040,25 +30040,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I35" t="n">
         <v>95.83643606459415</v>
@@ -30091,25 +30091,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="T35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="U35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="V35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Y35" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36">
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -30164,31 +30164,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15.9401497155857</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R36" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>348</v>
+        <v>268.2701978327065</v>
       </c>
       <c r="T36" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="U36" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="V36" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W36" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X36" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Y36" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30198,76 +30198,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>348</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G37" t="n">
-        <v>244.4127253005464</v>
+        <v>345</v>
       </c>
       <c r="H37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>295.316185202081</v>
+        <v>345</v>
       </c>
       <c r="L37" t="n">
-        <v>329.713201928271</v>
+        <v>345</v>
       </c>
       <c r="M37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="R37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="S37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="T37" t="n">
         <v>207.3278451947823</v>
       </c>
       <c r="U37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="V37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X37" t="n">
-        <v>348</v>
+        <v>294.7546971565684</v>
       </c>
       <c r="Y37" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30277,25 +30277,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I38" t="n">
         <v>95.83643606459415</v>
@@ -30325,28 +30325,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>162.4939254614603</v>
+        <v>162.493925461517</v>
       </c>
       <c r="S38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="T38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="U38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="V38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Y38" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39">
@@ -30356,28 +30356,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9867056863481</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>107.0629048726869</v>
+        <v>233.517993650618</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,28 +30404,28 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="S39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="T39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="U39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Y39" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40">
@@ -30435,76 +30435,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>348</v>
+        <v>286.5432149371638</v>
       </c>
       <c r="I40" t="n">
-        <v>183.8638507487257</v>
+        <v>157.6531277512658</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>215.192904948684</v>
+        <v>345</v>
       </c>
       <c r="L40" t="n">
-        <v>329.713201928271</v>
+        <v>345</v>
       </c>
       <c r="M40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="R40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="S40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="U40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="V40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Y40" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41">
@@ -30593,16 +30593,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
         <v>321</v>
@@ -30611,7 +30611,7 @@
         <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>321</v>
+        <v>224.1353878714273</v>
       </c>
       <c r="I42" t="n">
         <v>191.2065745705938</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>321</v>
@@ -30656,13 +30656,13 @@
         <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
       </c>
       <c r="Y42" t="n">
-        <v>189.8430359884416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -30699,7 +30699,7 @@
         <v>321</v>
       </c>
       <c r="K43" t="n">
-        <v>309.7843364833202</v>
+        <v>321</v>
       </c>
       <c r="L43" t="n">
         <v>321</v>
@@ -30726,7 +30726,7 @@
         <v>321</v>
       </c>
       <c r="T43" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="U43" t="n">
         <v>321</v>
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>189.8430359882683</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D45" t="n">
         <v>321</v>
@@ -30842,13 +30842,13 @@
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>147.1542359884949</v>
       </c>
       <c r="G45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>191.2065745705938</v>
@@ -30878,10 +30878,10 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
@@ -30890,7 +30890,7 @@
         <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>321</v>
@@ -30963,7 +30963,7 @@
         <v>321</v>
       </c>
       <c r="T46" t="n">
-        <v>309.7843364833203</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="U46" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4180904522613062</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.281768844221103</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>16.11843216080402</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>35.48490452261307</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>53.18267336683417</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>65.97780904522614</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>73.41302512562814</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>74.60092462311559</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>70.44353768844221</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>60.12192964824121</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>45.14906532663316</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>26.2628743718593</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.527236180904525</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.830190954773869</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03344723618090449</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2236981132075472</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.16045283018868</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.701886792452831</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>21.13456603773585</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>36.12233962264151</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>48.57094339622642</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>56.67999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>58.18015094339623</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>53.22347169811321</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>42.7165283018868</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.55486792452831</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.88890566037736</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.155094339622639</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9016603773584903</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01471698113207548</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1875409836065574</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.667409836065575</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.639868852459018</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.25914754098361</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.78885245901639</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.88222950819672</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>29.39790163934425</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.69888524590166</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>26.5080655737705</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.68222950819671</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.704</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.432524590163931</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.268327868852458</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8013114754098358</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01022950819672132</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4180904522613062</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.281768844221103</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>16.11843216080402</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>35.48490452261307</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>53.18267336683417</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>65.97780904522614</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>73.41302512562814</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>74.60092462311559</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>70.44353768844221</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>60.12192964824121</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>45.14906532663316</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>26.2628743718593</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.527236180904525</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.830190954773869</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03344723618090449</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2236981132075472</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16045283018868</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.701886792452831</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>21.13456603773585</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>36.12233962264151</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>48.57094339622642</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>56.67999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>58.18015094339623</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>53.22347169811321</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>42.7165283018868</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.55486792452831</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.88890566037736</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.155094339622639</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9016603773584903</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01471698113207548</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1875409836065574</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.667409836065575</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.639868852459018</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.25914754098361</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.78885245901639</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.88222950819672</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>29.39790163934425</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.69888524590166</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>26.5080655737705</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.68222950819671</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.704</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.432524590163931</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.268327868852458</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8013114754098358</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01022950819672132</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4180904522613062</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.281768844221103</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>16.11843216080402</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>35.48490452261307</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>53.18267336683417</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>65.97780904522614</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>73.41302512562814</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>74.60092462311559</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>70.44353768844221</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>60.12192964824121</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.14906532663316</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>26.2628743718593</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.527236180904525</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.830190954773869</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03344723618090449</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2236981132075472</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16045283018868</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.701886792452831</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>21.13456603773585</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>36.12233962264151</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>48.57094339622642</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>56.67999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>58.18015094339623</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>53.22347169811321</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>42.7165283018868</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.55486792452831</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.88890566037736</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.155094339622639</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9016603773584903</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01471698113207548</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1875409836065574</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.667409836065575</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.639868852459018</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.25914754098361</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.78885245901639</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.88222950819672</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>29.39790163934425</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.69888524590166</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>26.5080655737705</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.68222950819671</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.704</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.432524590163931</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.268327868852458</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8013114754098358</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01022950819672132</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34746,10 +34746,10 @@
         <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>53.18267336683419</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>65.97780904522619</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34758,13 +34758,13 @@
         <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1956681143497576</v>
+        <v>181.6174062160025</v>
       </c>
       <c r="P2" t="n">
-        <v>59.8348696075598</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>179.697868754919</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>146.3431722754116</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>227.2261942634328</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>319.8197527160896</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>143.6300421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>192.8067010520511</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>294.6804936008596</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>156.38253281654</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34883,31 +34883,31 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>3.183276392681392</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>4.334601350417529</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.89484816599702</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7767449691521</v>
+        <v>39.08222422535515</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0518382337388</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,25 +34980,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4418982775227391</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
-        <v>53.18267336683417</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>65.97780904522614</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="M5" t="n">
-        <v>239.0908400849562</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
         <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1956681143497576</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
         <v>374</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>146.3431722754116</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>227.2261942634328</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>322.6623187449134</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>143.6300421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>189.9641350232273</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>294.6804936008596</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>156.38253281654</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35117,34 +35117,34 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>70.80397629053127</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1436681420765</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.896283734447</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>148.0211513318891</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>4.33460135041755</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,19 +35165,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.89484816599703</v>
+        <v>40.86342193648883</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7767449691521</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>53.18267336683419</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>374</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>245.6756778001451</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1956681143497576</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>59.8348696075598</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>146.3431722754116</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>227.2261942634328</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>322.6623187449134</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>143.6300421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>192.8067010520511</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>291.8379275720357</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>156.38253281654</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,22 +35357,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>129.1412879722406</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>55.47027517437445</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35381,7 +35381,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,13 +35408,13 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35454,16 +35454,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L11" t="n">
-        <v>222.0407035175879</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M11" t="n">
-        <v>166.1869066997263</v>
+        <v>471.53813374078</v>
       </c>
       <c r="N11" t="n">
         <v>649</v>
@@ -35475,7 +35475,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35603,10 +35603,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H13" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I13" t="n">
         <v>163.3468722487342</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>102.456491288538</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U13" t="n">
         <v>170.0760349550503</v>
@@ -35657,7 +35657,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y13" t="n">
-        <v>33.53464715053764</v>
+        <v>22.31898363385807</v>
       </c>
     </row>
     <row r="14">
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K14" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
-        <v>222.0407035175879</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M14" t="n">
-        <v>220.2135479083921</v>
+        <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.518284494548912</v>
       </c>
       <c r="O14" t="n">
         <v>166.8217284158573</v>
@@ -35837,7 +35837,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>35.40148051557846</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G16" t="n">
         <v>76.58727469945357</v>
@@ -35849,7 +35849,7 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J16" t="n">
-        <v>330.3531823116332</v>
+        <v>319.1375187949537</v>
       </c>
       <c r="K16" t="n">
         <v>105.807095051316</v>
@@ -35931,13 +35931,13 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K17" t="n">
-        <v>596.491643285883</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L17" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>619.5578495768601</v>
       </c>
       <c r="N17" t="n">
         <v>649</v>
@@ -35946,7 +35946,7 @@
         <v>166.8217284158573</v>
       </c>
       <c r="P17" t="n">
-        <v>202.0463570447457</v>
+        <v>649</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36077,16 +36077,16 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H19" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I19" t="n">
         <v>163.3468722487342</v>
       </c>
       <c r="J19" t="n">
-        <v>319.1375187949537</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K19" t="n">
         <v>105.807095051316</v>
@@ -36119,7 +36119,7 @@
         <v>113.6721548052177</v>
       </c>
       <c r="U19" t="n">
-        <v>170.0760349550503</v>
+        <v>158.8603714383706</v>
       </c>
       <c r="V19" t="n">
         <v>121.8296897837838</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K20" t="n">
         <v>178.9801507537688</v>
       </c>
       <c r="L20" t="n">
-        <v>639.5521960497022</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>243.2797541993688</v>
       </c>
       <c r="O20" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P20" t="n">
-        <v>202.0463570447457</v>
+        <v>649</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33.88619966292134</v>
+        <v>22.6705361462418</v>
       </c>
       <c r="C22" t="n">
         <v>48.27475335195533</v>
@@ -36365,7 +36365,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X22" t="n">
-        <v>62.34069105321293</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
         <v>33.53464715053764</v>
@@ -36405,16 +36405,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L23" t="n">
-        <v>649.0000000000001</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M23" t="n">
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>169.5323468034705</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>166.8217284158573</v>
@@ -36423,7 +36423,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>417.5114925321143</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36642,16 +36642,16 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K26" t="n">
-        <v>650</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L26" t="n">
-        <v>222.0407035175879</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M26" t="n">
         <v>650</v>
       </c>
       <c r="N26" t="n">
-        <v>168.1465026593223</v>
+        <v>639.1663519055533</v>
       </c>
       <c r="O26" t="n">
         <v>166.8217284158573</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K29" t="n">
+        <v>178.9801507537688</v>
+      </c>
+      <c r="L29" t="n">
+        <v>222.040703517588</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>641.3194581162331</v>
+      </c>
+      <c r="O29" t="n">
         <v>650</v>
-      </c>
-      <c r="L29" t="n">
-        <v>222.0407035175879</v>
-      </c>
-      <c r="M29" t="n">
-        <v>650</v>
-      </c>
-      <c r="N29" t="n">
-        <v>168.1465026593223</v>
-      </c>
-      <c r="O29" t="n">
-        <v>166.8217284158573</v>
       </c>
       <c r="P29" t="n">
         <v>202.0463570447457</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37034,7 +37034,7 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J31" t="n">
-        <v>319.1375187949535</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K31" t="n">
         <v>105.807095051316</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U31" t="n">
         <v>170.0760349550503</v>
@@ -37116,16 +37116,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K32" t="n">
-        <v>650</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L32" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M32" t="n">
-        <v>598.4512392454789</v>
+        <v>650</v>
       </c>
       <c r="N32" t="n">
-        <v>650</v>
+        <v>474.4977297003759</v>
       </c>
       <c r="O32" t="n">
         <v>166.8217284158573</v>
@@ -37134,7 +37134,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37253,7 +37253,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D34" t="n">
-        <v>24.24811842776471</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E34" t="n">
         <v>40.01909516304346</v>
@@ -37313,7 +37313,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>73.55635456989245</v>
+        <v>62.34069105321269</v>
       </c>
       <c r="Y34" t="n">
         <v>33.53464715053764</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K35" t="n">
-        <v>178.9801507537689</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L35" t="n">
-        <v>441.6330041305915</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M35" t="n">
-        <v>548.0000000000083</v>
+        <v>559.0000000000089</v>
       </c>
       <c r="N35" t="n">
-        <v>548.0000000000083</v>
+        <v>369.8431195823557</v>
       </c>
       <c r="O35" t="n">
         <v>166.8217284158573</v>
@@ -37438,7 +37438,7 @@
         <v>437.5512810090644</v>
       </c>
       <c r="M36" t="n">
-        <v>214.8801731054748</v>
+        <v>258.4357286609758</v>
       </c>
       <c r="N36" t="n">
         <v>330.4251350143152</v>
@@ -37484,37 +37484,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>60.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>75.27475335195533</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>62.46378194444452</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>67.01909516304346</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>73.61714403225807</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>100.5872746994536</v>
       </c>
       <c r="H37" t="n">
-        <v>124.8403493082175</v>
+        <v>121.8403493082175</v>
       </c>
       <c r="I37" t="n">
-        <v>190.3468722487342</v>
+        <v>187.3468722487342</v>
       </c>
       <c r="J37" t="n">
         <v>9.353182311633219</v>
       </c>
       <c r="K37" t="n">
-        <v>80.12328025339698</v>
+        <v>129.807095051316</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>15.28679807172902</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,19 +37541,19 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>197.0760349550503</v>
+        <v>194.0760349550503</v>
       </c>
       <c r="V37" t="n">
-        <v>148.8296897837838</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>121.6271901612903</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>100.5563545698924</v>
+        <v>47.31105172646084</v>
       </c>
       <c r="Y37" t="n">
-        <v>60.53464715053764</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37596,10 +37596,10 @@
         <v>222.040703517588</v>
       </c>
       <c r="M38" t="n">
-        <v>548.0000000000229</v>
+        <v>559.0000000000234</v>
       </c>
       <c r="N38" t="n">
-        <v>548.0000000000229</v>
+        <v>241.1478561684746</v>
       </c>
       <c r="O38" t="n">
         <v>166.8217284158573</v>
@@ -37608,7 +37608,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q38" t="n">
-        <v>219.5923006129744</v>
+        <v>559.0000000000234</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37681,10 +37681,10 @@
         <v>330.4251350143152</v>
       </c>
       <c r="O39" t="n">
-        <v>357.7546056739056</v>
+        <v>420.5744747329351</v>
       </c>
       <c r="P39" t="n">
-        <v>257.4235516844645</v>
+        <v>238.1592381809363</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37721,37 +37721,37 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>60.88619966292134</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>75.27475335195533</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>62.46378194444452</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>67.01909516304346</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>73.61714403225807</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>103.5872746994536</v>
+        <v>100.5872746994536</v>
       </c>
       <c r="H40" t="n">
-        <v>124.8403493082175</v>
+        <v>63.38356424538127</v>
       </c>
       <c r="I40" t="n">
-        <v>26.21072299745991</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>9.353182311633219</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>129.807095051316</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>15.28679807172904</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>140.6721548052177</v>
+        <v>137.6721548052177</v>
       </c>
       <c r="U40" t="n">
-        <v>197.0760349550503</v>
+        <v>194.0760349550503</v>
       </c>
       <c r="V40" t="n">
-        <v>148.8296897837838</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>121.6271901612903</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>100.5563545698924</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>60.53464715053764</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37827,16 +37827,16 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K41" t="n">
-        <v>548.0000000000248</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L41" t="n">
-        <v>222.0407035175879</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M41" t="n">
-        <v>516.2677147806075</v>
+        <v>559.000000000038</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>369.8431195823263</v>
       </c>
       <c r="O41" t="n">
         <v>166.8217284158573</v>
@@ -37909,7 +37909,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L42" t="n">
-        <v>374.731411950035</v>
+        <v>418.286967505536</v>
       </c>
       <c r="M42" t="n">
         <v>277.7000421645042</v>
@@ -37973,10 +37973,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H43" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I43" t="n">
         <v>163.3468722487342</v>
@@ -37985,7 +37985,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K43" t="n">
-        <v>94.59143153463614</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>113.6721548052177</v>
+        <v>102.4564912885382</v>
       </c>
       <c r="U43" t="n">
         <v>170.0760349550503</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K44" t="n">
-        <v>548.0000000000247</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L44" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M44" t="n">
-        <v>548.0000000000665</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>398.5724513668741</v>
+        <v>536.6648479981548</v>
       </c>
       <c r="O44" t="n">
-        <v>166.8217284158573</v>
+        <v>559.0000000000671</v>
       </c>
       <c r="P44" t="n">
         <v>202.0463570447457</v>
@@ -38146,13 +38146,13 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L45" t="n">
-        <v>437.5512810090644</v>
+        <v>418.286967505536</v>
       </c>
       <c r="M45" t="n">
         <v>277.7000421645042</v>
       </c>
       <c r="N45" t="n">
-        <v>267.6052659554622</v>
+        <v>330.4251350143152</v>
       </c>
       <c r="O45" t="n">
         <v>420.5744747329351</v>
@@ -38210,10 +38210,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H46" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I46" t="n">
         <v>163.3468722487342</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>102.456491288538</v>
+        <v>102.4564912885382</v>
       </c>
       <c r="U46" t="n">
         <v>170.0760349550503</v>
